--- a/database/event/8292/event_8292_evp_summary.xlsx
+++ b/database/event/8292/event_8292_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.3615</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>6.6746</v>
       </c>
       <c r="D2" t="n">
         <v>4.1684</v>
@@ -545,7 +545,7 @@
         <v>7.4307</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.3654</v>
       </c>
       <c r="D3" t="n">
         <v>2.5805</v>
@@ -591,7 +591,7 @@
         <v>7.3977</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.346</v>
       </c>
       <c r="D4" t="n">
         <v>2.5671</v>
@@ -637,7 +637,7 @@
         <v>7.1652</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>4.2094</v>
       </c>
       <c r="D5" t="n">
         <v>2.4732</v>
@@ -683,7 +683,7 @@
         <v>7.1116</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4.1779</v>
       </c>
       <c r="D6" t="n">
         <v>2.4516</v>
@@ -729,7 +729,7 @@
         <v>6.5199</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.8303</v>
       </c>
       <c r="D7" t="n">
         <v>2.2125</v>
@@ -775,7 +775,7 @@
         <v>4.9641</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.9163</v>
       </c>
       <c r="D8" t="n">
         <v>1.584</v>
@@ -821,7 +821,7 @@
         <v>4.5735</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.6868</v>
       </c>
       <c r="D9" t="n">
         <v>1.4262</v>
@@ -867,7 +867,7 @@
         <v>4.3622</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.5627</v>
       </c>
       <c r="D10" t="n">
         <v>1.3409</v>
@@ -913,7 +913,7 @@
         <v>4.2924</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.5217</v>
       </c>
       <c r="D11" t="n">
         <v>1.3127</v>
@@ -959,7 +959,7 @@
         <v>3.9749</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.3352</v>
       </c>
       <c r="D12" t="n">
         <v>1.1844</v>
@@ -1005,7 +1005,7 @@
         <v>3.8897</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.2851</v>
       </c>
       <c r="D13" t="n">
         <v>1.15</v>
@@ -1051,7 +1051,7 @@
         <v>3.8345</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>2.2527</v>
       </c>
       <c r="D14" t="n">
         <v>1.1277</v>
@@ -1097,7 +1097,7 @@
         <v>3.7527</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>2.2046</v>
       </c>
       <c r="D15" t="n">
         <v>1.0946</v>
@@ -1143,7 +1143,7 @@
         <v>3.6283</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.1315</v>
       </c>
       <c r="D16" t="n">
         <v>1.0444</v>
@@ -1189,7 +1189,7 @@
         <v>3.5369</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>2.0779</v>
       </c>
       <c r="D17" t="n">
         <v>1.0075</v>
@@ -1235,7 +1235,7 @@
         <v>3.4484</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>2.0259</v>
       </c>
       <c r="D18" t="n">
         <v>0.9717</v>
@@ -1281,7 +1281,7 @@
         <v>3.3274</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.9548</v>
       </c>
       <c r="D19" t="n">
         <v>0.9228</v>
@@ -1327,7 +1327,7 @@
         <v>3.2098</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.8857</v>
       </c>
       <c r="D20" t="n">
         <v>0.8753</v>
@@ -1373,7 +1373,7 @@
         <v>3.1487</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.8498</v>
       </c>
       <c r="D21" t="n">
         <v>0.8506</v>
@@ -1419,7 +1419,7 @@
         <v>3.0323</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.7814</v>
       </c>
       <c r="D22" t="n">
         <v>0.8036</v>
@@ -1465,7 +1465,7 @@
         <v>2.9351</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.7243</v>
       </c>
       <c r="D23" t="n">
         <v>0.7644</v>
@@ -1511,7 +1511,7 @@
         <v>2.8591</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.6797</v>
       </c>
       <c r="D24" t="n">
         <v>0.7337</v>
@@ -1557,7 +1557,7 @@
         <v>2.7536</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.6177</v>
       </c>
       <c r="D25" t="n">
         <v>0.6909999999999999</v>
@@ -1603,7 +1603,7 @@
         <v>2.6002</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.5276</v>
       </c>
       <c r="D26" t="n">
         <v>0.6291</v>
@@ -1649,7 +1649,7 @@
         <v>2.478</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.4558</v>
       </c>
       <c r="D27" t="n">
         <v>0.5797</v>
@@ -1695,7 +1695,7 @@
         <v>2.1438</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.2594</v>
       </c>
       <c r="D28" t="n">
         <v>0.4447</v>
@@ -1741,7 +1741,7 @@
         <v>2.1164</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.2433</v>
       </c>
       <c r="D29" t="n">
         <v>0.4336</v>
@@ -1787,7 +1787,7 @@
         <v>1.9939</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.1714</v>
       </c>
       <c r="D30" t="n">
         <v>0.3841</v>
@@ -1833,7 +1833,7 @@
         <v>1.8408</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1.0814</v>
       </c>
       <c r="D31" t="n">
         <v>0.3223</v>
@@ -1879,7 +1879,7 @@
         <v>1.7301</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1.0164</v>
       </c>
       <c r="D32" t="n">
         <v>0.2776</v>
@@ -1925,7 +1925,7 @@
         <v>1.5956</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.9374</v>
       </c>
       <c r="D33" t="n">
         <v>0.2232</v>
@@ -1971,7 +1971,7 @@
         <v>1.4803</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.8696</v>
       </c>
       <c r="D34" t="n">
         <v>0.1766</v>
@@ -2017,7 +2017,7 @@
         <v>1.4282</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.839</v>
       </c>
       <c r="D35" t="n">
         <v>0.1556</v>
@@ -2063,7 +2063,7 @@
         <v>1.2703</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.7463</v>
       </c>
       <c r="D36" t="n">
         <v>0.09180000000000001</v>
@@ -2109,7 +2109,7 @@
         <v>1.2504</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.7346</v>
       </c>
       <c r="D37" t="n">
         <v>0.0838</v>
@@ -2155,7 +2155,7 @@
         <v>1.216</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.7144</v>
       </c>
       <c r="D38" t="n">
         <v>0.0699</v>
@@ -2201,7 +2201,7 @@
         <v>1.0797</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.6343</v>
       </c>
       <c r="D39" t="n">
         <v>0.0148</v>
@@ -2247,7 +2247,7 @@
         <v>1.0657</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.6261</v>
       </c>
       <c r="D40" t="n">
         <v>0.0092</v>
@@ -2293,7 +2293,7 @@
         <v>0.8772</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.5153</v>
       </c>
       <c r="D41" t="n">
         <v>-0.067</v>
@@ -2339,7 +2339,7 @@
         <v>0.7235</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.425</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1291</v>
@@ -2385,7 +2385,7 @@
         <v>0.6709000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3941</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1503</v>
@@ -2431,7 +2431,7 @@
         <v>0.6657999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.3911</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1524</v>
@@ -2477,7 +2477,7 @@
         <v>0.6589</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3871</v>
       </c>
       <c r="D45" t="n">
         <v>-0.1552</v>
@@ -2523,7 +2523,7 @@
         <v>0.5127</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3012</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2142</v>
@@ -2569,7 +2569,7 @@
         <v>0.4452</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.2615</v>
       </c>
       <c r="D47" t="n">
         <v>-0.2415</v>
@@ -2615,7 +2615,7 @@
         <v>0.3136</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1842</v>
       </c>
       <c r="D48" t="n">
         <v>-0.2947</v>
@@ -2661,7 +2661,7 @@
         <v>0.2347</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1379</v>
       </c>
       <c r="D49" t="n">
         <v>-0.3265</v>
@@ -2707,7 +2707,7 @@
         <v>0.0346</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.0203</v>
       </c>
       <c r="D50" t="n">
         <v>-0.4074</v>
@@ -2753,7 +2753,7 @@
         <v>-0.0558</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0328</v>
       </c>
       <c r="D51" t="n">
         <v>-0.4439</v>
@@ -2799,7 +2799,7 @@
         <v>-0.089</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0523</v>
       </c>
       <c r="D52" t="n">
         <v>-0.4573</v>
@@ -2845,7 +2845,7 @@
         <v>-0.2184</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.1283</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5096000000000001</v>
@@ -2891,7 +2891,7 @@
         <v>-0.2577</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.1514</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5255</v>
@@ -2937,7 +2937,7 @@
         <v>-0.2692</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1581</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5301</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2886</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1695</v>
       </c>
       <c r="D56" t="n">
         <v>-0.538</v>
@@ -3029,7 +3029,7 @@
         <v>-0.3168</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1861</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5493</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3958</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2325</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5813</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4747</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2789</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6131</v>
@@ -3167,7 +3167,7 @@
         <v>-0.586</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3443</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6581</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6051</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3555</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6657999999999999</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6509</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3824</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6843</v>
@@ -3305,7 +3305,7 @@
         <v>-0.6813</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4002</v>
       </c>
       <c r="D63" t="n">
         <v>-0.6966</v>
@@ -3351,7 +3351,7 @@
         <v>-0.6914</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4062</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7007</v>
@@ -3397,7 +3397,7 @@
         <v>-0.7496</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.4404</v>
       </c>
       <c r="D65" t="n">
         <v>-0.7242</v>
@@ -3443,7 +3443,7 @@
         <v>-0.9519</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.5592</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8058999999999999</v>
@@ -3489,7 +3489,7 @@
         <v>-1.0821</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.6357</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8585</v>
@@ -3535,7 +3535,7 @@
         <v>-1.4567</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.8558</v>
       </c>
       <c r="D68" t="n">
         <v>-1.0098</v>
@@ -3581,7 +3581,7 @@
         <v>-1.4787</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.8687</v>
       </c>
       <c r="D69" t="n">
         <v>-1.0187</v>
@@ -3627,7 +3627,7 @@
         <v>-1.5236</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.8951</v>
       </c>
       <c r="D70" t="n">
         <v>-1.0369</v>
@@ -3673,7 +3673,7 @@
         <v>-1.5521</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.9118000000000001</v>
       </c>
       <c r="D71" t="n">
         <v>-1.0484</v>
@@ -3719,7 +3719,7 @@
         <v>-1.5793</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.9278</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0594</v>
@@ -3765,7 +3765,7 @@
         <v>-1.6057</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.9433</v>
       </c>
       <c r="D73" t="n">
         <v>-1.07</v>
@@ -3811,7 +3811,7 @@
         <v>-1.6647</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.978</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0939</v>
@@ -3857,7 +3857,7 @@
         <v>-1.778</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.0445</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1396</v>
@@ -3903,7 +3903,7 @@
         <v>-1.9287</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.1331</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2005</v>
@@ -3949,7 +3949,7 @@
         <v>-1.9666</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.1553</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2158</v>
@@ -3995,7 +3995,7 @@
         <v>-1.9873</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1675</v>
       </c>
       <c r="D78" t="n">
         <v>-1.2242</v>
@@ -4041,7 +4041,7 @@
         <v>-2.2157</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.3017</v>
       </c>
       <c r="D79" t="n">
         <v>-1.3165</v>
@@ -4087,7 +4087,7 @@
         <v>-3.2574</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.9137</v>
       </c>
       <c r="D80" t="n">
         <v>-1.7373</v>
@@ -4133,7 +4133,7 @@
         <v>-3.5609</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.092</v>
       </c>
       <c r="D81" t="n">
         <v>-1.8599</v>

--- a/database/event/8292/event_8292_evp_summary.xlsx
+++ b/database/event/8292/event_8292_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>6.6746</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1684</v>
+        <v>4.0825</v>
       </c>
       <c r="E2" t="n">
         <v>11.3615</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4307</v>
+        <v>7.4142</v>
       </c>
       <c r="C3" t="n">
-        <v>4.3654</v>
+        <v>4.3557</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5805</v>
+        <v>2.5099</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4307</v>
+        <v>7.4142</v>
       </c>
       <c r="F3" t="n">
-        <v>5.8993</v>
+        <v>5.8828</v>
       </c>
       <c r="G3" t="n">
         <v>1.5314</v>
       </c>
       <c r="H3" t="n">
-        <v>6.9471</v>
+        <v>6.9211</v>
       </c>
       <c r="I3" t="n">
         <v>6.9794</v>
@@ -594,7 +594,7 @@
         <v>4.346</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5671</v>
+        <v>2.5033</v>
       </c>
       <c r="E4" t="n">
         <v>7.3977</v>
@@ -640,7 +640,7 @@
         <v>4.2094</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4732</v>
+        <v>2.4107</v>
       </c>
       <c r="E5" t="n">
         <v>7.1652</v>
@@ -686,7 +686,7 @@
         <v>4.1779</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4516</v>
+        <v>2.3894</v>
       </c>
       <c r="E6" t="n">
         <v>7.1116</v>
@@ -732,7 +732,7 @@
         <v>3.8303</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2125</v>
+        <v>2.1536</v>
       </c>
       <c r="E7" t="n">
         <v>6.5199</v>
@@ -778,7 +778,7 @@
         <v>2.9163</v>
       </c>
       <c r="D8" t="n">
-        <v>1.584</v>
+        <v>1.5338</v>
       </c>
       <c r="E8" t="n">
         <v>4.9641</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.5735</v>
+        <v>4.5621</v>
       </c>
       <c r="C9" t="n">
-        <v>2.6868</v>
+        <v>2.6801</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4262</v>
+        <v>1.3736</v>
       </c>
       <c r="E9" t="n">
-        <v>4.5735</v>
+        <v>4.5621</v>
       </c>
       <c r="F9" t="n">
-        <v>4.5219</v>
+        <v>4.5105</v>
       </c>
       <c r="G9" t="n">
         <v>0.0516</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7873</v>
+        <v>4.7695</v>
       </c>
       <c r="I9" t="n">
         <v>4.8096</v>
@@ -870,7 +870,7 @@
         <v>2.5627</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3409</v>
+        <v>1.294</v>
       </c>
       <c r="E10" t="n">
         <v>4.3622</v>
@@ -916,7 +916,7 @@
         <v>2.5217</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3127</v>
+        <v>1.2662</v>
       </c>
       <c r="E11" t="n">
         <v>4.2924</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.9749</v>
+        <v>3.9647</v>
       </c>
       <c r="C12" t="n">
-        <v>2.3352</v>
+        <v>2.3292</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1844</v>
+        <v>1.1356</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9749</v>
+        <v>3.9647</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7487</v>
+        <v>2.7385</v>
       </c>
       <c r="G12" t="n">
         <v>1.2262</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7487</v>
+        <v>2.7385</v>
       </c>
       <c r="I12" t="n">
         <v>2.7615</v>
@@ -1008,7 +1008,7 @@
         <v>2.2851</v>
       </c>
       <c r="D13" t="n">
-        <v>1.15</v>
+        <v>1.1057</v>
       </c>
       <c r="E13" t="n">
         <v>3.8897</v>
@@ -1054,7 +1054,7 @@
         <v>2.2527</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1277</v>
+        <v>1.0838</v>
       </c>
       <c r="E14" t="n">
         <v>3.8345</v>
@@ -1100,7 +1100,7 @@
         <v>2.2046</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0946</v>
+        <v>1.0512</v>
       </c>
       <c r="E15" t="n">
         <v>3.7527</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.6283</v>
+        <v>3.6181</v>
       </c>
       <c r="C16" t="n">
-        <v>2.1315</v>
+        <v>2.1256</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0444</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6283</v>
+        <v>3.6181</v>
       </c>
       <c r="F16" t="n">
-        <v>4.1908</v>
+        <v>4.1806</v>
       </c>
       <c r="G16" t="n">
         <v>-0.5625</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2681</v>
+        <v>4.2522</v>
       </c>
       <c r="I16" t="n">
         <v>4.2879</v>
@@ -1192,7 +1192,7 @@
         <v>2.0779</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0075</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="E17" t="n">
         <v>3.5369</v>
@@ -1238,7 +1238,7 @@
         <v>2.0259</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9717</v>
+        <v>0.9298999999999999</v>
       </c>
       <c r="E18" t="n">
         <v>3.4484</v>
@@ -1284,7 +1284,7 @@
         <v>1.9548</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9228</v>
+        <v>0.8817</v>
       </c>
       <c r="E19" t="n">
         <v>3.3274</v>
@@ -1330,7 +1330,7 @@
         <v>1.8857</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8753</v>
+        <v>0.8349</v>
       </c>
       <c r="E20" t="n">
         <v>3.2098</v>
@@ -1376,7 +1376,7 @@
         <v>1.8498</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8506</v>
+        <v>0.8105</v>
       </c>
       <c r="E21" t="n">
         <v>3.1487</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.0323</v>
+        <v>3.0201</v>
       </c>
       <c r="C22" t="n">
-        <v>1.7814</v>
+        <v>1.7742</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8036</v>
+        <v>0.7593</v>
       </c>
       <c r="E22" t="n">
-        <v>3.0323</v>
+        <v>3.0201</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2561</v>
+        <v>3.2439</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2238</v>
       </c>
       <c r="H22" t="n">
-        <v>3.2561</v>
+        <v>3.2439</v>
       </c>
       <c r="I22" t="n">
         <v>3.2712</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9351</v>
+        <v>2.921</v>
       </c>
       <c r="C23" t="n">
-        <v>1.7243</v>
+        <v>1.716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7644</v>
+        <v>0.7198</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9351</v>
+        <v>2.921</v>
       </c>
       <c r="F23" t="n">
-        <v>3.8008</v>
+        <v>3.7867</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8657</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8008</v>
+        <v>3.7867</v>
       </c>
       <c r="I23" t="n">
         <v>3.8185</v>
@@ -1514,7 +1514,7 @@
         <v>1.6797</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7337</v>
+        <v>0.6952</v>
       </c>
       <c r="E24" t="n">
         <v>2.8591</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.7536</v>
+        <v>2.7428</v>
       </c>
       <c r="C25" t="n">
-        <v>1.6177</v>
+        <v>1.6113</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6488</v>
       </c>
       <c r="E25" t="n">
-        <v>2.7536</v>
+        <v>2.7428</v>
       </c>
       <c r="F25" t="n">
-        <v>2.8881</v>
+        <v>2.8773</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1345</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8881</v>
+        <v>2.8773</v>
       </c>
       <c r="I25" t="n">
         <v>2.9015</v>
@@ -1606,7 +1606,7 @@
         <v>1.5276</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6291</v>
+        <v>0.592</v>
       </c>
       <c r="E26" t="n">
         <v>2.6002</v>
@@ -1652,7 +1652,7 @@
         <v>1.4558</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5797</v>
+        <v>0.5433</v>
       </c>
       <c r="E27" t="n">
         <v>2.478</v>
@@ -1698,7 +1698,7 @@
         <v>1.2594</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4447</v>
+        <v>0.4102</v>
       </c>
       <c r="E28" t="n">
         <v>2.1438</v>
@@ -1744,7 +1744,7 @@
         <v>1.2433</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4336</v>
+        <v>0.3993</v>
       </c>
       <c r="E29" t="n">
         <v>2.1164</v>
@@ -1790,7 +1790,7 @@
         <v>1.1714</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3841</v>
+        <v>0.3505</v>
       </c>
       <c r="E30" t="n">
         <v>1.9939</v>
@@ -1836,7 +1836,7 @@
         <v>1.0814</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3223</v>
+        <v>0.2895</v>
       </c>
       <c r="E31" t="n">
         <v>1.8408</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.7301</v>
+        <v>1.7208</v>
       </c>
       <c r="C32" t="n">
-        <v>1.0164</v>
+        <v>1.0109</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2776</v>
+        <v>0.2417</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7301</v>
+        <v>1.7208</v>
       </c>
       <c r="F32" t="n">
-        <v>2.4749</v>
+        <v>2.4656</v>
       </c>
       <c r="G32" t="n">
         <v>-0.7448</v>
       </c>
       <c r="H32" t="n">
-        <v>2.4749</v>
+        <v>2.4656</v>
       </c>
       <c r="I32" t="n">
         <v>2.4864</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.5956</v>
+        <v>1.5865</v>
       </c>
       <c r="C33" t="n">
-        <v>0.9374</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2232</v>
+        <v>0.1882</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5956</v>
+        <v>1.5865</v>
       </c>
       <c r="F33" t="n">
-        <v>2.4321</v>
+        <v>2.423</v>
       </c>
       <c r="G33" t="n">
         <v>-0.8365</v>
       </c>
       <c r="H33" t="n">
-        <v>2.4321</v>
+        <v>2.423</v>
       </c>
       <c r="I33" t="n">
         <v>2.4434</v>
@@ -1974,7 +1974,7 @@
         <v>0.8696</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1766</v>
+        <v>0.1458</v>
       </c>
       <c r="E34" t="n">
         <v>1.4803</v>
@@ -2020,7 +2020,7 @@
         <v>0.839</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1556</v>
+        <v>0.1251</v>
       </c>
       <c r="E35" t="n">
         <v>1.4282</v>
@@ -2066,7 +2066,7 @@
         <v>0.7463</v>
       </c>
       <c r="D36" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.0622</v>
       </c>
       <c r="E36" t="n">
         <v>1.2703</v>
@@ -2112,7 +2112,7 @@
         <v>0.7346</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0838</v>
+        <v>0.0542</v>
       </c>
       <c r="E37" t="n">
         <v>1.2504</v>
@@ -2158,7 +2158,7 @@
         <v>0.7144</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0699</v>
+        <v>0.0405</v>
       </c>
       <c r="E38" t="n">
         <v>1.216</v>
@@ -2204,7 +2204,7 @@
         <v>0.6343</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0148</v>
+        <v>-0.0138</v>
       </c>
       <c r="E39" t="n">
         <v>1.0797</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.0657</v>
+        <v>1.0583</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6261</v>
+        <v>0.6217</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0092</v>
+        <v>-0.0223</v>
       </c>
       <c r="E40" t="n">
-        <v>1.0657</v>
+        <v>1.0583</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9748</v>
+        <v>1.9674</v>
       </c>
       <c r="G40" t="n">
         <v>-0.9091</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9748</v>
+        <v>1.9674</v>
       </c>
       <c r="I40" t="n">
         <v>1.984</v>
@@ -2296,7 +2296,7 @@
         <v>0.5153</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.067</v>
+        <v>-0.0944</v>
       </c>
       <c r="E41" t="n">
         <v>0.8772</v>
@@ -2336,25 +2336,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7235</v>
+        <v>0.7207</v>
       </c>
       <c r="C42" t="n">
-        <v>0.425</v>
+        <v>0.4234</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1291</v>
+        <v>-0.1568</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7235</v>
+        <v>0.7207</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7417</v>
       </c>
       <c r="G42" t="n">
         <v>-0.021</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.7417</v>
       </c>
       <c r="I42" t="n">
         <v>0.7479</v>
@@ -2388,7 +2388,7 @@
         <v>0.3941</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1503</v>
+        <v>-0.1766</v>
       </c>
       <c r="E43" t="n">
         <v>0.6709000000000001</v>
@@ -2434,7 +2434,7 @@
         <v>0.3911</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1524</v>
+        <v>-0.1787</v>
       </c>
       <c r="E44" t="n">
         <v>0.6657999999999999</v>
@@ -2480,7 +2480,7 @@
         <v>0.3871</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1552</v>
+        <v>-0.1814</v>
       </c>
       <c r="E45" t="n">
         <v>0.6589</v>
@@ -2526,7 +2526,7 @@
         <v>0.3012</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2142</v>
+        <v>-0.2397</v>
       </c>
       <c r="E46" t="n">
         <v>0.5127</v>
@@ -2572,7 +2572,7 @@
         <v>0.2615</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2415</v>
+        <v>-0.2665</v>
       </c>
       <c r="E47" t="n">
         <v>0.4452</v>
@@ -2618,7 +2618,7 @@
         <v>0.1842</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2947</v>
+        <v>-0.319</v>
       </c>
       <c r="E48" t="n">
         <v>0.3136</v>
@@ -2664,7 +2664,7 @@
         <v>0.1379</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3265</v>
+        <v>-0.3504</v>
       </c>
       <c r="E49" t="n">
         <v>0.2347</v>
@@ -2710,7 +2710,7 @@
         <v>0.0203</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4074</v>
+        <v>-0.4301</v>
       </c>
       <c r="E50" t="n">
         <v>0.0346</v>
@@ -2756,7 +2756,7 @@
         <v>-0.0328</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4439</v>
+        <v>-0.4661</v>
       </c>
       <c r="E51" t="n">
         <v>-0.0558</v>
@@ -2796,25 +2796,25 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.089</v>
+        <v>-0.0852</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0523</v>
+        <v>-0.0501</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4573</v>
+        <v>-0.4779</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.089</v>
+        <v>-0.0852</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.0158</v>
+        <v>-1.012</v>
       </c>
       <c r="G52" t="n">
         <v>0.9268</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.0158</v>
+        <v>-1.012</v>
       </c>
       <c r="I52" t="n">
         <v>-1.0205</v>
@@ -2848,7 +2848,7 @@
         <v>-0.1283</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.5309</v>
       </c>
       <c r="E53" t="n">
         <v>-0.2184</v>
@@ -2888,25 +2888,25 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2577</v>
+        <v>-0.2591</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1514</v>
+        <v>-0.1522</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5255</v>
+        <v>-0.5471</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2577</v>
+        <v>-0.2591</v>
       </c>
       <c r="F54" t="n">
-        <v>0.375</v>
+        <v>0.3736</v>
       </c>
       <c r="G54" t="n">
         <v>-0.6327</v>
       </c>
       <c r="H54" t="n">
-        <v>0.375</v>
+        <v>0.3736</v>
       </c>
       <c r="I54" t="n">
         <v>0.3767</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1581</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5301</v>
+        <v>-0.5512</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2692</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1695</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.538</v>
+        <v>-0.5589</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2886</v>
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3168</v>
+        <v>-0.3193</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1861</v>
+        <v>-0.1876</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5493</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3168</v>
+        <v>-0.3193</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6832</v>
+        <v>0.6807</v>
       </c>
       <c r="G57" t="n">
         <v>-1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.6832</v>
+        <v>0.6807</v>
       </c>
       <c r="I57" t="n">
         <v>0.6864</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2325</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5813</v>
+        <v>-0.6016</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3958</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2789</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6131</v>
+        <v>-0.633</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4747</v>
@@ -3170,7 +3170,7 @@
         <v>-0.3443</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6581</v>
+        <v>-0.6774</v>
       </c>
       <c r="E60" t="n">
         <v>-0.586</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3555</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6657999999999999</v>
+        <v>-0.6850000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6051</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3824</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6843</v>
+        <v>-0.7032</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6509</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4002</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6966</v>
+        <v>-0.7153</v>
       </c>
       <c r="E63" t="n">
         <v>-0.6813</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4062</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7007</v>
+        <v>-0.7194</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6914</v>
@@ -3400,7 +3400,7 @@
         <v>-0.4404</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7242</v>
+        <v>-0.7426</v>
       </c>
       <c r="E65" t="n">
         <v>-0.7496</v>
@@ -3446,7 +3446,7 @@
         <v>-0.5592</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8058999999999999</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="E66" t="n">
         <v>-0.9519</v>
@@ -3492,7 +3492,7 @@
         <v>-0.6357</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8585</v>
+        <v>-0.875</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0821</v>
@@ -3538,7 +3538,7 @@
         <v>-0.8558</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0098</v>
+        <v>-1.0243</v>
       </c>
       <c r="E68" t="n">
         <v>-1.4567</v>
@@ -3584,7 +3584,7 @@
         <v>-0.8687</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0187</v>
+        <v>-1.033</v>
       </c>
       <c r="E69" t="n">
         <v>-1.4787</v>
@@ -3630,7 +3630,7 @@
         <v>-0.8951</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0369</v>
+        <v>-1.0509</v>
       </c>
       <c r="E70" t="n">
         <v>-1.5236</v>
@@ -3676,7 +3676,7 @@
         <v>-0.9118000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0484</v>
+        <v>-1.0623</v>
       </c>
       <c r="E71" t="n">
         <v>-1.5521</v>
@@ -3722,7 +3722,7 @@
         <v>-0.9278</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0594</v>
+        <v>-1.0731</v>
       </c>
       <c r="E72" t="n">
         <v>-1.5793</v>
@@ -3768,7 +3768,7 @@
         <v>-0.9433</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.07</v>
+        <v>-1.0836</v>
       </c>
       <c r="E73" t="n">
         <v>-1.6057</v>
@@ -3814,7 +3814,7 @@
         <v>-0.978</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0939</v>
+        <v>-1.1071</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6647</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0445</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1396</v>
+        <v>-1.1523</v>
       </c>
       <c r="E75" t="n">
         <v>-1.778</v>
@@ -3906,7 +3906,7 @@
         <v>-1.1331</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2005</v>
+        <v>-1.2123</v>
       </c>
       <c r="E76" t="n">
         <v>-1.9287</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1553</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2158</v>
+        <v>-1.2274</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9666</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1675</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2242</v>
+        <v>-1.2357</v>
       </c>
       <c r="E78" t="n">
         <v>-1.9873</v>
@@ -4044,7 +4044,7 @@
         <v>-1.3017</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.3165</v>
+        <v>-1.3266</v>
       </c>
       <c r="E79" t="n">
         <v>-2.2157</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.2574</v>
+        <v>-3.2482</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.9137</v>
+        <v>-1.9082</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7373</v>
+        <v>-1.738</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.2574</v>
+        <v>-3.2482</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.4687</v>
+        <v>-2.4595</v>
       </c>
       <c r="G80" t="n">
         <v>-0.7887</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.4687</v>
+        <v>-2.4595</v>
       </c>
       <c r="I80" t="n">
         <v>-2.4802</v>
@@ -4136,7 +4136,7 @@
         <v>-2.092</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8599</v>
+        <v>-1.8626</v>
       </c>
       <c r="E81" t="n">
         <v>-3.5609</v>

--- a/database/event/8292/event_8292_evp_summary.xlsx
+++ b/database/event/8292/event_8292_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.0955</v>
+        <v>11.4872</v>
       </c>
       <c r="C2" t="n">
-        <v>6.5184</v>
+        <v>6.7485</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4267</v>
+        <v>4.5173</v>
       </c>
       <c r="E2" t="n">
-        <v>11.0955</v>
+        <v>11.4872</v>
       </c>
       <c r="F2" t="n">
-        <v>4.7572</v>
+        <v>4.7484</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3383</v>
+        <v>6.2959</v>
       </c>
       <c r="H2" t="n">
-        <v>7.687</v>
+        <v>7.6679</v>
       </c>
       <c r="I2" t="n">
-        <v>7.687</v>
+        <v>7.6679</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3383</v>
+        <v>6.2959</v>
       </c>
       <c r="K2" t="n">
         <v>134</v>
@@ -529,7 +529,7 @@
         <v>163</v>
       </c>
       <c r="M2" t="n">
-        <v>14.0253</v>
+        <v>13.9638</v>
       </c>
       <c r="N2" t="n">
         <v>297</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.775</v>
+        <v>8.3081</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5676</v>
+        <v>4.8808</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9151</v>
+        <v>3.0972</v>
       </c>
       <c r="E3" t="n">
-        <v>7.775</v>
+        <v>8.3081</v>
       </c>
       <c r="F3" t="n">
-        <v>5.5081</v>
+        <v>5.5084</v>
       </c>
       <c r="G3" t="n">
         <v>2.2669</v>
       </c>
       <c r="H3" t="n">
-        <v>9.3306</v>
+        <v>9.331099999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>9.3306</v>
+        <v>9.331099999999999</v>
       </c>
       <c r="J3" t="n">
         <v>2.2669</v>
@@ -575,7 +575,7 @@
         <v>150</v>
       </c>
       <c r="M3" t="n">
-        <v>11.5975</v>
+        <v>11.598</v>
       </c>
       <c r="N3" t="n">
         <v>271</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.609</v>
+        <v>8.006</v>
       </c>
       <c r="C4" t="n">
-        <v>4.4701</v>
+        <v>4.7034</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8396</v>
+        <v>2.9623</v>
       </c>
       <c r="E4" t="n">
-        <v>7.609</v>
+        <v>8.006</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5531</v>
+        <v>5.8236</v>
       </c>
       <c r="G4" t="n">
-        <v>5.0559</v>
+        <v>1.4775</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8631</v>
+        <v>10.0212</v>
       </c>
       <c r="I4" t="n">
-        <v>2.8631</v>
+        <v>10.2794</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0559</v>
+        <v>1.4775</v>
       </c>
       <c r="K4" t="n">
-        <v>134</v>
+        <v>236</v>
       </c>
       <c r="L4" t="n">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="M4" t="n">
-        <v>7.919</v>
+        <v>11.7569</v>
       </c>
       <c r="N4" t="n">
-        <v>297</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.2939</v>
+        <v>7.6883</v>
       </c>
       <c r="C5" t="n">
-        <v>4.285</v>
+        <v>4.5167</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6961</v>
+        <v>2.8204</v>
       </c>
       <c r="E5" t="n">
-        <v>7.2939</v>
+        <v>7.6883</v>
       </c>
       <c r="F5" t="n">
-        <v>5.8157</v>
+        <v>2.5531</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4782</v>
+        <v>5.0566</v>
       </c>
       <c r="H5" t="n">
-        <v>10.0038</v>
+        <v>2.863</v>
       </c>
       <c r="I5" t="n">
-        <v>10.2616</v>
+        <v>2.863</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4782</v>
+        <v>5.0566</v>
       </c>
       <c r="K5" t="n">
-        <v>236</v>
+        <v>134</v>
       </c>
       <c r="L5" t="n">
-        <v>69</v>
+        <v>163</v>
       </c>
       <c r="M5" t="n">
-        <v>11.7398</v>
+        <v>7.919600000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>305</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.7178</v>
+        <v>6.957</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9466</v>
+        <v>4.0871</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4339</v>
+        <v>2.4937</v>
       </c>
       <c r="E6" t="n">
-        <v>6.7178</v>
+        <v>6.957</v>
       </c>
       <c r="F6" t="n">
         <v>3.5073</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2105</v>
+        <v>3.2346</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9515</v>
+        <v>4.9514</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9515</v>
+        <v>4.9514</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2105</v>
+        <v>3.2346</v>
       </c>
       <c r="K6" t="n">
         <v>134</v>
@@ -713,7 +713,7 @@
         <v>163</v>
       </c>
       <c r="M6" t="n">
-        <v>8.162000000000001</v>
+        <v>8.186</v>
       </c>
       <c r="N6" t="n">
         <v>297</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8597</v>
+        <v>6.0697</v>
       </c>
       <c r="C7" t="n">
-        <v>3.4424</v>
+        <v>3.5658</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0433</v>
+        <v>2.0974</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8597</v>
+        <v>6.0697</v>
       </c>
       <c r="F7" t="n">
-        <v>3.1054</v>
+        <v>3.1053</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7543</v>
+        <v>2.799</v>
       </c>
       <c r="H7" t="n">
-        <v>4.0718</v>
+        <v>4.0716</v>
       </c>
       <c r="I7" t="n">
-        <v>4.0718</v>
+        <v>4.0716</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7543</v>
+        <v>2.799</v>
       </c>
       <c r="K7" t="n">
         <v>194</v>
@@ -759,7 +759,7 @@
         <v>199</v>
       </c>
       <c r="M7" t="n">
-        <v>6.8261</v>
+        <v>6.8706</v>
       </c>
       <c r="N7" t="n">
         <v>393</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.0298</v>
+        <v>4.9391</v>
       </c>
       <c r="C8" t="n">
-        <v>2.9549</v>
+        <v>2.9016</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6655</v>
+        <v>1.5924</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0298</v>
+        <v>4.9391</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4029</v>
+        <v>2.4088</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6269</v>
+        <v>2.6088</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5342</v>
+        <v>2.5471</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5342</v>
+        <v>2.5471</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6269</v>
+        <v>2.6088</v>
       </c>
       <c r="K8" t="n">
         <v>134</v>
@@ -805,7 +805,7 @@
         <v>163</v>
       </c>
       <c r="M8" t="n">
-        <v>5.161099999999999</v>
+        <v>5.1559</v>
       </c>
       <c r="N8" t="n">
         <v>297</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6489</v>
+        <v>4.8264</v>
       </c>
       <c r="C9" t="n">
-        <v>2.7311</v>
+        <v>2.8354</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4921</v>
+        <v>1.542</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6489</v>
+        <v>4.8264</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9948</v>
+        <v>2.9872</v>
       </c>
       <c r="G9" t="n">
         <v>1.6541</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8297</v>
+        <v>3.8131</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8297</v>
+        <v>3.8131</v>
       </c>
       <c r="J9" t="n">
         <v>1.6541</v>
@@ -851,7 +851,7 @@
         <v>150</v>
       </c>
       <c r="M9" t="n">
-        <v>5.4838</v>
+        <v>5.4672</v>
       </c>
       <c r="N9" t="n">
         <v>271</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0277</v>
+        <v>4.3294</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3662</v>
+        <v>2.5434</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2093</v>
+        <v>1.32</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0277</v>
+        <v>4.3294</v>
       </c>
       <c r="F10" t="n">
-        <v>4.4088</v>
+        <v>4.4093</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3811</v>
+        <v>-0.3819</v>
       </c>
       <c r="H10" t="n">
-        <v>6.9246</v>
+        <v>6.9256</v>
       </c>
       <c r="I10" t="n">
-        <v>6.9246</v>
+        <v>6.9256</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3811</v>
+        <v>-0.3819</v>
       </c>
       <c r="K10" t="n">
         <v>205</v>
@@ -897,7 +897,7 @@
         <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>6.5435</v>
+        <v>6.5437</v>
       </c>
       <c r="N10" t="n">
         <v>305</v>
@@ -906,231 +906,231 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>w0nderful</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0204</v>
+        <v>4.0164</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3619</v>
+        <v>2.3595</v>
       </c>
       <c r="D11" t="n">
-        <v>1.206</v>
+        <v>1.1802</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0204</v>
+        <v>4.0164</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3771</v>
+        <v>2.6766</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6433</v>
+        <v>1.264</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3771</v>
+        <v>3.1334</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3771</v>
+        <v>3.2141</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6433</v>
+        <v>1.264</v>
       </c>
       <c r="K11" t="n">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="L11" t="n">
-        <v>163</v>
+        <v>38</v>
       </c>
       <c r="M11" t="n">
-        <v>4.0204</v>
+        <v>4.4781</v>
       </c>
       <c r="N11" t="n">
-        <v>297</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.0087</v>
+        <v>3.9623</v>
       </c>
       <c r="C12" t="n">
-        <v>2.355</v>
+        <v>2.3278</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2006</v>
+        <v>1.1561</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0087</v>
+        <v>3.9623</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3523</v>
+        <v>4.5506</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6564</v>
+        <v>-0.9161</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4235</v>
+        <v>7.2348</v>
       </c>
       <c r="I12" t="n">
-        <v>2.4235</v>
+        <v>7.2348</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6564</v>
+        <v>-0.9161</v>
       </c>
       <c r="K12" t="n">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="M12" t="n">
-        <v>4.0799</v>
+        <v>6.3187</v>
       </c>
       <c r="N12" t="n">
-        <v>305</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>w0nderful</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.9405</v>
+        <v>3.9039</v>
       </c>
       <c r="C13" t="n">
-        <v>2.315</v>
+        <v>2.2935</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1696</v>
+        <v>1.13</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9405</v>
+        <v>3.9039</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6765</v>
+        <v>2.3424</v>
       </c>
       <c r="G13" t="n">
-        <v>1.264</v>
+        <v>1.6622</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1331</v>
+        <v>2.4019</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2138</v>
+        <v>2.4019</v>
       </c>
       <c r="J13" t="n">
-        <v>1.264</v>
+        <v>1.6622</v>
       </c>
       <c r="K13" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L13" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>4.4778</v>
+        <v>4.0641</v>
       </c>
       <c r="N13" t="n">
-        <v>242</v>
+        <v>305</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.627</v>
+        <v>3.7476</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1308</v>
+        <v>2.2016</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0269</v>
+        <v>1.0602</v>
       </c>
       <c r="E14" t="n">
-        <v>3.627</v>
+        <v>3.7476</v>
       </c>
       <c r="F14" t="n">
-        <v>4.5431</v>
+        <v>3.3967</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9161</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2184</v>
+        <v>4.7093</v>
       </c>
       <c r="I14" t="n">
-        <v>7.2184</v>
+        <v>4.7093</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9161</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>257</v>
+        <v>299</v>
       </c>
       <c r="L14" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>6.3023</v>
+        <v>4.7093</v>
       </c>
       <c r="N14" t="n">
-        <v>334</v>
+        <v>299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.4654</v>
+        <v>3.7429</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0358</v>
+        <v>2.1989</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9533</v>
+        <v>1.0581</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4654</v>
+        <v>3.7429</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1869</v>
+        <v>0.3516</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2785</v>
+        <v>3.569</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2501</v>
+        <v>0.3516</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2501</v>
+        <v>0.3516</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2785</v>
+        <v>3.569</v>
       </c>
       <c r="K15" t="n">
-        <v>194</v>
+        <v>134</v>
       </c>
       <c r="L15" t="n">
-        <v>199</v>
+        <v>163</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5286</v>
+        <v>3.9206</v>
       </c>
       <c r="N15" t="n">
-        <v>393</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.4628</v>
+        <v>3.5567</v>
       </c>
       <c r="C16" t="n">
-        <v>2.0343</v>
+        <v>2.0895</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.9749</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4628</v>
+        <v>3.5567</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4458</v>
+        <v>3.4604</v>
       </c>
       <c r="G16" t="n">
-        <v>0.017</v>
+        <v>0.0167</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8169</v>
+        <v>4.8488</v>
       </c>
       <c r="I16" t="n">
-        <v>4.941</v>
+        <v>4.9737</v>
       </c>
       <c r="J16" t="n">
-        <v>0.017</v>
+        <v>0.0167</v>
       </c>
       <c r="K16" t="n">
         <v>283</v>
@@ -1173,7 +1173,7 @@
         <v>44</v>
       </c>
       <c r="M16" t="n">
-        <v>4.958</v>
+        <v>4.9904</v>
       </c>
       <c r="N16" t="n">
         <v>327</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.421</v>
+        <v>3.4083</v>
       </c>
       <c r="C17" t="n">
-        <v>2.0098</v>
+        <v>2.0023</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9331</v>
+        <v>0.9086</v>
       </c>
       <c r="E17" t="n">
-        <v>3.421</v>
+        <v>3.4083</v>
       </c>
       <c r="F17" t="n">
-        <v>3.421</v>
+        <v>3.4209</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7625</v>
+        <v>4.7624</v>
       </c>
       <c r="I17" t="n">
-        <v>4.7625</v>
+        <v>4.7624</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.7625</v>
+        <v>4.7624</v>
       </c>
       <c r="N17" t="n">
         <v>272</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.3969</v>
+        <v>3.3611</v>
       </c>
       <c r="C18" t="n">
-        <v>1.9956</v>
+        <v>1.9746</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9221</v>
+        <v>0.8875</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3969</v>
+        <v>3.3611</v>
       </c>
       <c r="F18" t="n">
-        <v>3.3969</v>
+        <v>3.1769</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.2783</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7099</v>
+        <v>4.2284</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7099</v>
+        <v>4.2284</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.2783</v>
       </c>
       <c r="K18" t="n">
-        <v>299</v>
+        <v>194</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M18" t="n">
-        <v>4.7099</v>
+        <v>4.506699999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>299</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.2245</v>
+        <v>3.3192</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8943</v>
+        <v>1.95</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8437</v>
+        <v>0.8688</v>
       </c>
       <c r="E19" t="n">
-        <v>3.2245</v>
+        <v>3.3192</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2245</v>
+        <v>3.1285</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3324</v>
+        <v>4.1224</v>
       </c>
       <c r="I19" t="n">
-        <v>4.3324</v>
+        <v>4.1224</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3324</v>
+        <v>4.1224</v>
       </c>
       <c r="N19" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.1308</v>
+        <v>3.2873</v>
       </c>
       <c r="C20" t="n">
-        <v>1.8393</v>
+        <v>1.9312</v>
       </c>
       <c r="D20" t="n">
-        <v>0.801</v>
+        <v>0.8545</v>
       </c>
       <c r="E20" t="n">
-        <v>3.1308</v>
+        <v>3.2873</v>
       </c>
       <c r="F20" t="n">
-        <v>3.1308</v>
+        <v>3.131</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1274</v>
+        <v>4.1279</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1274</v>
+        <v>4.1279</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1274</v>
+        <v>4.1279</v>
       </c>
       <c r="N20" t="n">
         <v>240</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.1287</v>
+        <v>3.2789</v>
       </c>
       <c r="C21" t="n">
-        <v>1.838</v>
+        <v>1.9263</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>0.8508</v>
       </c>
       <c r="E21" t="n">
-        <v>3.1287</v>
+        <v>3.2789</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1287</v>
+        <v>3.5316</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.4126</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1228</v>
+        <v>5.0046</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1228</v>
+        <v>5.1336</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.4126</v>
       </c>
       <c r="K21" t="n">
-        <v>299</v>
+        <v>204</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1228</v>
+        <v>4.721</v>
       </c>
       <c r="N21" t="n">
-        <v>299</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.1189</v>
+        <v>3.1875</v>
       </c>
       <c r="C22" t="n">
-        <v>1.8323</v>
+        <v>1.8726</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7956</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1189</v>
+        <v>3.1875</v>
       </c>
       <c r="F22" t="n">
-        <v>3.5315</v>
+        <v>3.2243</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4126</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>5.0043</v>
+        <v>4.3321</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1333</v>
+        <v>4.3321</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4126</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>204</v>
+        <v>272</v>
       </c>
       <c r="L22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.7207</v>
+        <v>4.3321</v>
       </c>
       <c r="N22" t="n">
-        <v>242</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.9882</v>
+        <v>3.0932</v>
       </c>
       <c r="C23" t="n">
-        <v>1.7555</v>
+        <v>1.8172</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7361</v>
+        <v>0.7678</v>
       </c>
       <c r="E23" t="n">
-        <v>2.9882</v>
+        <v>3.0932</v>
       </c>
       <c r="F23" t="n">
-        <v>3.1724</v>
+        <v>3.1721</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1842</v>
+        <v>-0.1845</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2185</v>
+        <v>4.2178</v>
       </c>
       <c r="I23" t="n">
-        <v>4.3272</v>
+        <v>4.3265</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1842</v>
+        <v>-0.1845</v>
       </c>
       <c r="K23" t="n">
         <v>283</v>
@@ -1495,7 +1495,7 @@
         <v>44</v>
       </c>
       <c r="M23" t="n">
-        <v>4.143000000000001</v>
+        <v>4.142</v>
       </c>
       <c r="N23" t="n">
         <v>327</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.8821</v>
+        <v>2.9848</v>
       </c>
       <c r="C24" t="n">
-        <v>1.6932</v>
+        <v>1.7535</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6878</v>
+        <v>0.7194</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8821</v>
+        <v>2.9848</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8821</v>
+        <v>2.8828</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5831</v>
+        <v>3.5847</v>
       </c>
       <c r="I24" t="n">
-        <v>3.5831</v>
+        <v>3.5847</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5831</v>
+        <v>3.5847</v>
       </c>
       <c r="N24" t="n">
         <v>188</v>
@@ -1550,185 +1550,185 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.8053</v>
+        <v>2.9488</v>
       </c>
       <c r="C25" t="n">
-        <v>1.6481</v>
+        <v>1.7324</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6528</v>
+        <v>0.7033</v>
       </c>
       <c r="E25" t="n">
-        <v>2.8053</v>
+        <v>2.9488</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8043</v>
+        <v>3.3725</v>
       </c>
       <c r="G25" t="n">
-        <v>2.001</v>
+        <v>-0.581</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8043</v>
+        <v>4.6563</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8043</v>
+        <v>4.7763</v>
       </c>
       <c r="J25" t="n">
-        <v>2.001</v>
+        <v>-0.581</v>
       </c>
       <c r="K25" t="n">
-        <v>121</v>
+        <v>236</v>
       </c>
       <c r="L25" t="n">
-        <v>150</v>
+        <v>69</v>
       </c>
       <c r="M25" t="n">
-        <v>2.8053</v>
+        <v>4.1953</v>
       </c>
       <c r="N25" t="n">
-        <v>271</v>
+        <v>305</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.7687</v>
+        <v>2.8849</v>
       </c>
       <c r="C26" t="n">
-        <v>1.6266</v>
+        <v>1.6948</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6362</v>
+        <v>0.6748</v>
       </c>
       <c r="E26" t="n">
-        <v>2.7687</v>
+        <v>2.8849</v>
       </c>
       <c r="F26" t="n">
-        <v>3.3728</v>
+        <v>2.7066</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.6041</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6571</v>
+        <v>3.1989</v>
       </c>
       <c r="I26" t="n">
-        <v>4.7771</v>
+        <v>3.1989</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6041</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>236</v>
+        <v>335</v>
       </c>
       <c r="L26" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4.173</v>
+        <v>3.1989</v>
       </c>
       <c r="N26" t="n">
-        <v>305</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.7442</v>
+        <v>2.6692</v>
       </c>
       <c r="C27" t="n">
-        <v>1.6122</v>
+        <v>1.5681</v>
       </c>
       <c r="D27" t="n">
-        <v>0.625</v>
+        <v>0.5785</v>
       </c>
       <c r="E27" t="n">
-        <v>2.7442</v>
+        <v>2.6692</v>
       </c>
       <c r="F27" t="n">
-        <v>2.7347</v>
+        <v>0.8046</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0095</v>
+        <v>2.001</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2605</v>
+        <v>0.8046</v>
       </c>
       <c r="I27" t="n">
-        <v>3.3445</v>
+        <v>0.8046</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0095</v>
+        <v>2.001</v>
       </c>
       <c r="K27" t="n">
-        <v>236</v>
+        <v>121</v>
       </c>
       <c r="L27" t="n">
-        <v>69</v>
+        <v>150</v>
       </c>
       <c r="M27" t="n">
-        <v>3.354</v>
+        <v>2.8056</v>
       </c>
       <c r="N27" t="n">
-        <v>305</v>
+        <v>271</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.7007</v>
+        <v>2.6438</v>
       </c>
       <c r="C28" t="n">
-        <v>1.5866</v>
+        <v>1.5532</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6052</v>
+        <v>0.5671</v>
       </c>
       <c r="E28" t="n">
-        <v>2.7007</v>
+        <v>2.6438</v>
       </c>
       <c r="F28" t="n">
-        <v>2.7007</v>
+        <v>2.7345</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>3.186</v>
+        <v>3.2601</v>
       </c>
       <c r="I28" t="n">
-        <v>3.186</v>
+        <v>3.3441</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>335</v>
+        <v>236</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="M28" t="n">
-        <v>3.186</v>
+        <v>3.3534</v>
       </c>
       <c r="N28" t="n">
-        <v>335</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29">
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.6604</v>
+        <v>2.6117</v>
       </c>
       <c r="C29" t="n">
-        <v>1.5629</v>
+        <v>1.5343</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5869</v>
+        <v>0.5528</v>
       </c>
       <c r="E29" t="n">
-        <v>2.6604</v>
+        <v>2.6117</v>
       </c>
       <c r="F29" t="n">
         <v>2.773</v>
@@ -1756,10 +1756,10 @@
         <v>-0.1126</v>
       </c>
       <c r="H29" t="n">
-        <v>3.3444</v>
+        <v>3.3442</v>
       </c>
       <c r="I29" t="n">
-        <v>3.3444</v>
+        <v>3.3442</v>
       </c>
       <c r="J29" t="n">
         <v>-0.1126</v>
@@ -1771,7 +1771,7 @@
         <v>77</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2318</v>
+        <v>3.2316</v>
       </c>
       <c r="N29" t="n">
         <v>334</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.487</v>
+        <v>2.5846</v>
       </c>
       <c r="C30" t="n">
-        <v>1.4611</v>
+        <v>1.5184</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5079</v>
+        <v>0.5407</v>
       </c>
       <c r="E30" t="n">
-        <v>2.487</v>
+        <v>2.5846</v>
       </c>
       <c r="F30" t="n">
-        <v>2.3721</v>
+        <v>2.3535</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1149</v>
+        <v>0.1389</v>
       </c>
       <c r="H30" t="n">
-        <v>2.4668</v>
+        <v>2.4262</v>
       </c>
       <c r="I30" t="n">
-        <v>2.4668</v>
+        <v>2.4262</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1149</v>
+        <v>0.1389</v>
       </c>
       <c r="K30" t="n">
         <v>205</v>
@@ -1817,7 +1817,7 @@
         <v>100</v>
       </c>
       <c r="M30" t="n">
-        <v>2.5817</v>
+        <v>2.5651</v>
       </c>
       <c r="N30" t="n">
         <v>305</v>
@@ -1826,219 +1826,219 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.4429</v>
+        <v>2.5555</v>
       </c>
       <c r="C31" t="n">
-        <v>1.4352</v>
+        <v>1.5013</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4879</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>2.4429</v>
+        <v>2.5555</v>
       </c>
       <c r="F31" t="n">
-        <v>2.6191</v>
+        <v>2.8634</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1762</v>
+        <v>-0.5201</v>
       </c>
       <c r="H31" t="n">
-        <v>3.0075</v>
+        <v>3.5421</v>
       </c>
       <c r="I31" t="n">
-        <v>3.0075</v>
+        <v>3.6334</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1762</v>
+        <v>-0.5201</v>
       </c>
       <c r="K31" t="n">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="L31" t="n">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="M31" t="n">
-        <v>2.8313</v>
+        <v>3.1133</v>
       </c>
       <c r="N31" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.44</v>
+        <v>2.5222</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4334</v>
+        <v>1.4817</v>
       </c>
       <c r="D32" t="n">
-        <v>0.4865</v>
+        <v>0.5128</v>
       </c>
       <c r="E32" t="n">
-        <v>2.44</v>
+        <v>2.5222</v>
       </c>
       <c r="F32" t="n">
-        <v>2.44</v>
+        <v>2.6185</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.1762</v>
       </c>
       <c r="H32" t="n">
-        <v>2.6154</v>
+        <v>3.0061</v>
       </c>
       <c r="I32" t="n">
-        <v>2.6154</v>
+        <v>3.0061</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.1762</v>
       </c>
       <c r="K32" t="n">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M32" t="n">
-        <v>2.6154</v>
+        <v>2.8299</v>
       </c>
       <c r="N32" t="n">
-        <v>240</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.3484</v>
+        <v>2.3875</v>
       </c>
       <c r="C33" t="n">
-        <v>1.3796</v>
+        <v>1.4026</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4448</v>
+        <v>0.4526</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3484</v>
+        <v>2.3875</v>
       </c>
       <c r="F33" t="n">
-        <v>2.8685</v>
+        <v>1.5234</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.5201</v>
+        <v>0.821</v>
       </c>
       <c r="H33" t="n">
-        <v>3.5532</v>
+        <v>1.5234</v>
       </c>
       <c r="I33" t="n">
-        <v>3.6448</v>
+        <v>1.5234</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.5201</v>
+        <v>0.821</v>
       </c>
       <c r="K33" t="n">
-        <v>204</v>
+        <v>257</v>
       </c>
       <c r="L33" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1247</v>
+        <v>2.3444</v>
       </c>
       <c r="N33" t="n">
-        <v>242</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.3205</v>
+        <v>2.3316</v>
       </c>
       <c r="C34" t="n">
-        <v>1.3632</v>
+        <v>1.3698</v>
       </c>
       <c r="D34" t="n">
-        <v>0.4321</v>
+        <v>0.4277</v>
       </c>
       <c r="E34" t="n">
-        <v>2.3205</v>
+        <v>2.3316</v>
       </c>
       <c r="F34" t="n">
-        <v>1.4995</v>
+        <v>2.4394</v>
       </c>
       <c r="G34" t="n">
-        <v>0.821</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.4995</v>
+        <v>2.6141</v>
       </c>
       <c r="I34" t="n">
-        <v>1.4995</v>
+        <v>2.6141</v>
       </c>
       <c r="J34" t="n">
-        <v>0.821</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="L34" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2.3205</v>
+        <v>2.6141</v>
       </c>
       <c r="N34" t="n">
-        <v>334</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.1912</v>
+        <v>2.14</v>
       </c>
       <c r="C35" t="n">
-        <v>1.2873</v>
+        <v>1.2572</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3733</v>
+        <v>0.3421</v>
       </c>
       <c r="E35" t="n">
-        <v>2.1912</v>
+        <v>2.14</v>
       </c>
       <c r="F35" t="n">
-        <v>2.4571</v>
+        <v>1.5468</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.2659</v>
+        <v>0.6085</v>
       </c>
       <c r="H35" t="n">
-        <v>2.6529</v>
+        <v>1.5468</v>
       </c>
       <c r="I35" t="n">
-        <v>2.6529</v>
+        <v>1.5468</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.2659</v>
+        <v>0.6085</v>
       </c>
       <c r="K35" t="n">
         <v>194</v>
@@ -2047,7 +2047,7 @@
         <v>199</v>
       </c>
       <c r="M35" t="n">
-        <v>2.387</v>
+        <v>2.1553</v>
       </c>
       <c r="N35" t="n">
         <v>393</v>
@@ -2056,35 +2056,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.1494</v>
+        <v>2.1318</v>
       </c>
       <c r="C36" t="n">
-        <v>1.2627</v>
+        <v>1.2524</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3542</v>
+        <v>0.3384</v>
       </c>
       <c r="E36" t="n">
-        <v>2.1494</v>
+        <v>2.1318</v>
       </c>
       <c r="F36" t="n">
-        <v>1.5422</v>
+        <v>2.4693</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6072</v>
+        <v>-0.2624</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5422</v>
+        <v>2.6797</v>
       </c>
       <c r="I36" t="n">
-        <v>1.5422</v>
+        <v>2.6797</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6072</v>
+        <v>-0.2624</v>
       </c>
       <c r="K36" t="n">
         <v>194</v>
@@ -2093,7 +2093,7 @@
         <v>199</v>
       </c>
       <c r="M36" t="n">
-        <v>2.1494</v>
+        <v>2.4173</v>
       </c>
       <c r="N36" t="n">
         <v>393</v>
@@ -2102,231 +2102,231 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.0684</v>
+        <v>2.0924</v>
       </c>
       <c r="C37" t="n">
-        <v>1.2151</v>
+        <v>1.2292</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3174</v>
+        <v>0.3208</v>
       </c>
       <c r="E37" t="n">
-        <v>2.0684</v>
+        <v>2.0924</v>
       </c>
       <c r="F37" t="n">
-        <v>2.6841</v>
+        <v>1.8668</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6157</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3.1496</v>
+        <v>1.8668</v>
       </c>
       <c r="I37" t="n">
-        <v>3.2308</v>
+        <v>1.8668</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6157</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.6151</v>
+        <v>1.8668</v>
       </c>
       <c r="N37" t="n">
-        <v>242</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.8586</v>
+        <v>1.8812</v>
       </c>
       <c r="C38" t="n">
-        <v>1.0919</v>
+        <v>1.1052</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2219</v>
+        <v>0.2265</v>
       </c>
       <c r="E38" t="n">
-        <v>1.8586</v>
+        <v>1.8812</v>
       </c>
       <c r="F38" t="n">
-        <v>1.8586</v>
+        <v>2.6842</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.6157</v>
       </c>
       <c r="H38" t="n">
-        <v>1.8586</v>
+        <v>3.1499</v>
       </c>
       <c r="I38" t="n">
-        <v>1.8586</v>
+        <v>3.2311</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.6157</v>
       </c>
       <c r="K38" t="n">
-        <v>166</v>
+        <v>204</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M38" t="n">
-        <v>1.8586</v>
+        <v>2.6154</v>
       </c>
       <c r="N38" t="n">
-        <v>166</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.7894</v>
+        <v>1.7805</v>
       </c>
       <c r="C39" t="n">
-        <v>1.0512</v>
+        <v>1.046</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1904</v>
+        <v>0.1815</v>
       </c>
       <c r="E39" t="n">
-        <v>1.7894</v>
+        <v>1.7805</v>
       </c>
       <c r="F39" t="n">
-        <v>1.4994</v>
+        <v>2.3843</v>
       </c>
       <c r="G39" t="n">
-        <v>0.29</v>
+        <v>-0.6058</v>
       </c>
       <c r="H39" t="n">
-        <v>1.4994</v>
+        <v>2.4935</v>
       </c>
       <c r="I39" t="n">
-        <v>1.538</v>
+        <v>2.5578</v>
       </c>
       <c r="J39" t="n">
-        <v>0.29</v>
+        <v>-0.6058</v>
       </c>
       <c r="K39" t="n">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="L39" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="M39" t="n">
-        <v>1.828</v>
+        <v>1.952</v>
       </c>
       <c r="N39" t="n">
-        <v>305</v>
+        <v>327</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.7612</v>
+        <v>1.7503</v>
       </c>
       <c r="C40" t="n">
-        <v>1.0347</v>
+        <v>1.0283</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1775</v>
+        <v>0.168</v>
       </c>
       <c r="E40" t="n">
-        <v>1.7612</v>
+        <v>1.7503</v>
       </c>
       <c r="F40" t="n">
-        <v>2.3842</v>
+        <v>1.743</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.623</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>2.4933</v>
+        <v>1.743</v>
       </c>
       <c r="I40" t="n">
-        <v>2.5576</v>
+        <v>1.743</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.623</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>283</v>
+        <v>194</v>
       </c>
       <c r="L40" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9346</v>
+        <v>1.743</v>
       </c>
       <c r="N40" t="n">
-        <v>327</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.743</v>
+        <v>1.6597</v>
       </c>
       <c r="C41" t="n">
-        <v>1.024</v>
+        <v>0.975</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1692</v>
+        <v>0.1275</v>
       </c>
       <c r="E41" t="n">
-        <v>1.743</v>
+        <v>1.6597</v>
       </c>
       <c r="F41" t="n">
-        <v>1.743</v>
+        <v>0.5061</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="H41" t="n">
-        <v>1.743</v>
+        <v>0.5061</v>
       </c>
       <c r="I41" t="n">
-        <v>1.743</v>
+        <v>0.5061</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1.1089</v>
       </c>
       <c r="K41" t="n">
         <v>194</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="M41" t="n">
-        <v>1.743</v>
+        <v>1.615</v>
       </c>
       <c r="N41" t="n">
-        <v>194</v>
+        <v>393</v>
       </c>
     </row>
     <row r="42">
@@ -2336,16 +2336,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.6735</v>
+        <v>1.6164</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9831</v>
+        <v>0.9496</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1376</v>
+        <v>0.1082</v>
       </c>
       <c r="E42" t="n">
-        <v>1.6735</v>
+        <v>1.6164</v>
       </c>
       <c r="F42" t="n">
         <v>1.6735</v>
@@ -2378,47 +2378,47 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.6153</v>
+        <v>1.583</v>
       </c>
       <c r="C43" t="n">
-        <v>0.949</v>
+        <v>0.93</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1111</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>1.6153</v>
+        <v>1.583</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5062</v>
+        <v>1.4989</v>
       </c>
       <c r="G43" t="n">
-        <v>1.1091</v>
+        <v>0.2796</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5062</v>
+        <v>1.4989</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5062</v>
+        <v>1.5375</v>
       </c>
       <c r="J43" t="n">
-        <v>1.1091</v>
+        <v>0.2796</v>
       </c>
       <c r="K43" t="n">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="L43" t="n">
-        <v>199</v>
+        <v>69</v>
       </c>
       <c r="M43" t="n">
-        <v>1.6153</v>
+        <v>1.8171</v>
       </c>
       <c r="N43" t="n">
-        <v>393</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44">
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.5542</v>
+        <v>1.5682</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9131</v>
+        <v>0.9213</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0833</v>
+        <v>0.0867</v>
       </c>
       <c r="E44" t="n">
-        <v>1.5542</v>
+        <v>1.5682</v>
       </c>
       <c r="F44" t="n">
-        <v>1.5542</v>
+        <v>1.5138</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>1.5542</v>
+        <v>1.5138</v>
       </c>
       <c r="I44" t="n">
-        <v>1.5542</v>
+        <v>1.5138</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1.5542</v>
+        <v>1.5138</v>
       </c>
       <c r="N44" t="n">
         <v>188</v>
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.3035</v>
+        <v>1.3752</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7658</v>
+        <v>0.8079</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.0308</v>
+        <v>0.0005</v>
       </c>
       <c r="E45" t="n">
-        <v>1.3035</v>
+        <v>1.3752</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3035</v>
+        <v>1.3034</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.3035</v>
+        <v>1.3034</v>
       </c>
       <c r="I45" t="n">
-        <v>1.3035</v>
+        <v>1.3034</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.3035</v>
+        <v>1.3034</v>
       </c>
       <c r="N45" t="n">
         <v>272</v>
@@ -2516,139 +2516,139 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>magixx</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9099</v>
+        <v>0.9694</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5345</v>
+        <v>0.5695</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.21</v>
+        <v>-0.1808</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9099</v>
+        <v>0.9694</v>
       </c>
       <c r="F46" t="n">
-        <v>1.4416</v>
+        <v>0.8731</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.5317</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1.4416</v>
+        <v>0.8731</v>
       </c>
       <c r="I46" t="n">
-        <v>1.4416</v>
+        <v>0.8731</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.5317</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="L46" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.9099</v>
+        <v>0.8731</v>
       </c>
       <c r="N46" t="n">
-        <v>271</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8731</v>
+        <v>0.9048</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5129</v>
+        <v>0.5316</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2268</v>
+        <v>-0.2097</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8731</v>
+        <v>0.9048</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8731</v>
+        <v>0.8364</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8731</v>
+        <v>0.8364</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8731</v>
+        <v>0.8364</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.8731</v>
+        <v>0.8364</v>
       </c>
       <c r="N47" t="n">
-        <v>194</v>
+        <v>240</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8531</v>
+        <v>0.7572</v>
       </c>
       <c r="C48" t="n">
-        <v>0.5012</v>
+        <v>0.4448</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2359</v>
+        <v>-0.2756</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8531</v>
+        <v>0.7572</v>
       </c>
       <c r="F48" t="n">
-        <v>0.8531</v>
+        <v>0.6142</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8531</v>
+        <v>0.6142</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8531</v>
+        <v>0.6142</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8531</v>
+        <v>0.6142</v>
       </c>
       <c r="N48" t="n">
-        <v>240</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49">
@@ -2658,31 +2658,31 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.852</v>
+        <v>0.7479</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4394</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2364</v>
+        <v>-0.2797</v>
       </c>
       <c r="E49" t="n">
-        <v>0.852</v>
+        <v>0.7479</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.1236</v>
+        <v>-0.1342</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9756</v>
+        <v>0.9746</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1236</v>
+        <v>-0.1342</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1268</v>
+        <v>-0.1377</v>
       </c>
       <c r="J49" t="n">
-        <v>0.9756</v>
+        <v>0.9746</v>
       </c>
       <c r="K49" t="n">
         <v>283</v>
@@ -2691,7 +2691,7 @@
         <v>44</v>
       </c>
       <c r="M49" t="n">
-        <v>0.8488</v>
+        <v>0.8369</v>
       </c>
       <c r="N49" t="n">
         <v>327</v>
@@ -2700,35 +2700,35 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>chopper</t>
+          <t>magixx</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.7386</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3805</v>
+        <v>0.4339</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3294</v>
+        <v>-0.2839</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.7386</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.2784</v>
+        <v>1.4419</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9261</v>
+        <v>-0.5317</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.2784</v>
+        <v>1.4419</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2784</v>
+        <v>1.4419</v>
       </c>
       <c r="J50" t="n">
-        <v>0.9261</v>
+        <v>-0.5317</v>
       </c>
       <c r="K50" t="n">
         <v>121</v>
@@ -2737,7 +2737,7 @@
         <v>150</v>
       </c>
       <c r="M50" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.9102</v>
       </c>
       <c r="N50" t="n">
         <v>271</v>
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.636</v>
+        <v>0.5532</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3736</v>
+        <v>0.325</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3347</v>
+        <v>-0.3667</v>
       </c>
       <c r="E51" t="n">
-        <v>0.636</v>
+        <v>0.5532</v>
       </c>
       <c r="F51" t="n">
-        <v>0.636</v>
+        <v>0.6359</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.636</v>
+        <v>0.6359</v>
       </c>
       <c r="I51" t="n">
-        <v>0.636</v>
+        <v>0.6359</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -2783,7 +2783,7 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.636</v>
+        <v>0.6359</v>
       </c>
       <c r="N51" t="n">
         <v>272</v>
@@ -2792,47 +2792,47 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>chopper</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6138</v>
+        <v>0.5148</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3606</v>
+        <v>0.3024</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3448</v>
+        <v>-0.3839</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6138</v>
+        <v>0.5148</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6138</v>
+        <v>-0.2781</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.9261</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6138</v>
+        <v>-0.2781</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6138</v>
+        <v>-0.2781</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>0.9261</v>
       </c>
       <c r="K52" t="n">
-        <v>178</v>
+        <v>121</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6138</v>
+        <v>0.648</v>
       </c>
       <c r="N52" t="n">
-        <v>178</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53">
@@ -2842,28 +2842,28 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5444</v>
+        <v>0.4745</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3198</v>
+        <v>0.2788</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3764</v>
+        <v>-0.4019</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5444</v>
+        <v>0.4745</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5444</v>
+        <v>0.5565</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5444</v>
+        <v>0.5565</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5444</v>
+        <v>0.5565</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2875,7 +2875,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5444</v>
+        <v>0.5565</v>
       </c>
       <c r="N53" t="n">
         <v>272</v>
@@ -2884,967 +2884,967 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5029</v>
+        <v>0.3568</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2954</v>
+        <v>0.2096</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.3953</v>
+        <v>-0.4544</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5029</v>
+        <v>0.3568</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5029</v>
+        <v>1.1591</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-0.8596</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5029</v>
+        <v>1.1591</v>
       </c>
       <c r="I54" t="n">
-        <v>0.5029</v>
+        <v>1.189</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-0.8596</v>
       </c>
       <c r="K54" t="n">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>0.5029</v>
+        <v>0.3294</v>
       </c>
       <c r="N54" t="n">
-        <v>194</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3877</v>
+        <v>0.3526</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2278</v>
+        <v>0.2071</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4477</v>
+        <v>-0.4563</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3877</v>
+        <v>0.3526</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7493</v>
+        <v>0.5029</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.3616</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.7493</v>
+        <v>0.5029</v>
       </c>
       <c r="I55" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.5029</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.3616</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>283</v>
+        <v>194</v>
       </c>
       <c r="L55" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.407</v>
+        <v>0.5029</v>
       </c>
       <c r="N55" t="n">
-        <v>327</v>
+        <v>194</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2992</v>
+        <v>0.2315</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1758</v>
+        <v>0.136</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.488</v>
+        <v>-0.5104</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2992</v>
+        <v>0.2315</v>
       </c>
       <c r="F56" t="n">
-        <v>1.1588</v>
+        <v>0.7489</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.8596</v>
+        <v>-0.3624</v>
       </c>
       <c r="H56" t="n">
-        <v>1.1588</v>
+        <v>0.7489</v>
       </c>
       <c r="I56" t="n">
-        <v>1.1887</v>
+        <v>0.7682</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.8596</v>
+        <v>-0.3624</v>
       </c>
       <c r="K56" t="n">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="L56" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M56" t="n">
-        <v>0.3291000000000001</v>
+        <v>0.4058</v>
       </c>
       <c r="N56" t="n">
-        <v>242</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2717</v>
+        <v>0.2013</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1596</v>
+        <v>0.1183</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.5239</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2717</v>
+        <v>0.2013</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.0607</v>
+        <v>0.2015</v>
       </c>
       <c r="G57" t="n">
-        <v>1.3324</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.0607</v>
+        <v>0.2015</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.0607</v>
+        <v>0.2015</v>
       </c>
       <c r="J57" t="n">
-        <v>1.3324</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>205</v>
+        <v>335</v>
       </c>
       <c r="L57" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2717000000000001</v>
+        <v>0.2015</v>
       </c>
       <c r="N57" t="n">
-        <v>305</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2111</v>
+        <v>0.0965</v>
       </c>
       <c r="C58" t="n">
-        <v>0.124</v>
+        <v>0.0567</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5281</v>
+        <v>-0.5707</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2111</v>
+        <v>0.0965</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2111</v>
+        <v>-0.0201</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2111</v>
+        <v>-0.0201</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2111</v>
+        <v>-0.0201</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>335</v>
+        <v>178</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.2111</v>
+        <v>-0.0201</v>
       </c>
       <c r="N58" t="n">
-        <v>335</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1495</v>
+        <v>0.06</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0878</v>
+        <v>0.0352</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5561</v>
+        <v>-0.587</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1495</v>
+        <v>0.06</v>
       </c>
       <c r="F59" t="n">
-        <v>0.1495</v>
+        <v>-1.0601</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1.2978</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1495</v>
+        <v>-1.0601</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1495</v>
+        <v>-1.0601</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1.2978</v>
       </c>
       <c r="K59" t="n">
-        <v>299</v>
+        <v>205</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1495</v>
+        <v>0.2377</v>
       </c>
       <c r="N59" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ag1l</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0183</v>
+        <v>-0.0323</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0108</v>
+        <v>-0.019</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6159</v>
+        <v>-0.6282</v>
       </c>
       <c r="E60" t="n">
-        <v>0.0183</v>
+        <v>-0.0323</v>
       </c>
       <c r="F60" t="n">
-        <v>0.0183</v>
+        <v>0.1492</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.0183</v>
+        <v>0.1492</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0183</v>
+        <v>0.1492</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>188</v>
+        <v>299</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0.0183</v>
+        <v>0.1492</v>
       </c>
       <c r="N60" t="n">
-        <v>188</v>
+        <v>299</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.0203</v>
+        <v>-0.0784</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0119</v>
+        <v>-0.0461</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6334</v>
+        <v>-0.6488</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0203</v>
+        <v>-0.0784</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0203</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.0203</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.0203</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.0203</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>kauez</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.0527</v>
+        <v>-0.1371</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.031</v>
+        <v>-0.0805</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6482</v>
+        <v>-0.6751</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0527</v>
+        <v>-0.1371</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0527</v>
+        <v>-0.2508</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.0527</v>
+        <v>-0.2508</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0527</v>
+        <v>-0.2508</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.0527</v>
+        <v>-0.2508</v>
       </c>
       <c r="N62" t="n">
-        <v>194</v>
+        <v>178</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Ag1l</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1404</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0551</v>
+        <v>-0.0825</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.6669</v>
+        <v>-0.6765</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1404</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0025</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0025</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0025</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>240</v>
+        <v>188</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0025</v>
       </c>
       <c r="N63" t="n">
-        <v>240</v>
+        <v>188</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>kauez</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.2034</v>
+        <v>-0.2541</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1195</v>
+        <v>-0.1493</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7168</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.2034</v>
+        <v>-0.2541</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.2034</v>
+        <v>-0.0527</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2034</v>
+        <v>-0.0527</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2034</v>
+        <v>-0.0527</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>240</v>
+        <v>194</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.2034</v>
+        <v>-0.0527</v>
       </c>
       <c r="N64" t="n">
-        <v>240</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>saffee</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.2404</v>
+        <v>-0.2671</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.1412</v>
+        <v>-0.1569</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7336</v>
+        <v>-0.7331</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.2404</v>
+        <v>-0.2671</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.2404</v>
+        <v>-0.3743</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.2404</v>
+        <v>-0.3743</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2404</v>
+        <v>-0.3743</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.2404</v>
+        <v>-0.3743</v>
       </c>
       <c r="N65" t="n">
-        <v>178</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.3633</v>
+        <v>-0.3049</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.2134</v>
+        <v>-0.1791</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7896</v>
+        <v>-0.75</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.3633</v>
+        <v>-0.3049</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.3633</v>
+        <v>-0.1942</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.3633</v>
+        <v>-0.1942</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3633</v>
+        <v>-0.1942</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.3633</v>
+        <v>-0.1942</v>
       </c>
       <c r="N66" t="n">
-        <v>178</v>
+        <v>240</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>saffee</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.373</v>
+        <v>-0.419</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.2191</v>
+        <v>-0.2462</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.794</v>
+        <v>-0.801</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.373</v>
+        <v>-0.419</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.373</v>
+        <v>-0.4526</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.373</v>
+        <v>-0.4526</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.373</v>
+        <v>-0.4526</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>166</v>
+        <v>335</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.373</v>
+        <v>-0.4526</v>
       </c>
       <c r="N67" t="n">
-        <v>166</v>
+        <v>335</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.4733</v>
+        <v>-0.5856</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.2781</v>
+        <v>-0.344</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8397</v>
+        <v>-0.8754</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.4733</v>
+        <v>-0.5856</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4681</v>
+        <v>-0.3632</v>
       </c>
       <c r="G68" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.4681</v>
+        <v>-0.3632</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4681</v>
+        <v>-0.3632</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="L68" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.4733</v>
+        <v>-0.3632</v>
       </c>
       <c r="N68" t="n">
-        <v>305</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.4816</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.2829</v>
+        <v>-0.4042</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8434</v>
+        <v>-0.9211</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.4816</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.4816</v>
+        <v>0.4689</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-0.9327</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.4816</v>
+        <v>0.4689</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4816</v>
+        <v>0.4689</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>-0.9327</v>
       </c>
       <c r="K69" t="n">
-        <v>335</v>
+        <v>205</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.4816</v>
+        <v>-0.4638</v>
       </c>
       <c r="N69" t="n">
-        <v>335</v>
+        <v>305</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AZUWU</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.9415</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.4646</v>
+        <v>-0.5531</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9842</v>
+        <v>-1.0344</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.9415</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.8784</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.8784</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.8784</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>188</v>
+        <v>166</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.8784</v>
       </c>
       <c r="N70" t="n">
-        <v>188</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>AZUWU</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.886</v>
+        <v>-1.1011</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5205</v>
+        <v>-0.6469</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0275</v>
+        <v>-1.1057</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.886</v>
+        <v>-1.1011</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.886</v>
+        <v>-0.7902</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.886</v>
+        <v>-0.7902</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.886</v>
+        <v>-0.7902</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.886</v>
+        <v>-0.7902</v>
       </c>
       <c r="N71" t="n">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>sl3nd</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.8982</v>
+        <v>-1.1774</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.6917</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0331</v>
+        <v>-1.1397</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.8982</v>
+        <v>-1.1774</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.8982</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.8982</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.8982</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.8982</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="N72" t="n">
-        <v>335</v>
+        <v>299</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>sl3nd</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.9789</v>
+        <v>-1.1854</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.6964</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0698</v>
+        <v>-1.1433</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.9789</v>
+        <v>-1.1854</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.9789</v>
+        <v>-1.0277</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.9789</v>
+        <v>-1.0277</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.9789</v>
+        <v>-1.0277</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>299</v>
+        <v>166</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.9789</v>
+        <v>-1.0277</v>
       </c>
       <c r="N73" t="n">
-        <v>299</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0425</v>
+        <v>-1.1963</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.7028</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0988</v>
+        <v>-1.1482</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0425</v>
+        <v>-1.1963</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.0425</v>
+        <v>-0.9077</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.0425</v>
+        <v>-0.9077</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.0425</v>
+        <v>-0.9077</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>166</v>
+        <v>335</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.0425</v>
+        <v>-0.9077</v>
       </c>
       <c r="N74" t="n">
-        <v>166</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75">
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.0956</v>
+        <v>-1.2653</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.7433</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1229</v>
+        <v>-1.179</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.0956</v>
+        <v>-1.2653</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.0956</v>
+        <v>-1.0958</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.0956</v>
+        <v>-1.0958</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.0956</v>
+        <v>-1.0958</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.0956</v>
+        <v>-1.0958</v>
       </c>
       <c r="N75" t="n">
         <v>335</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.1767</v>
+        <v>-1.2779</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6913</v>
+        <v>-0.7507</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.1599</v>
+        <v>-1.1846</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.1767</v>
+        <v>-1.2779</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.1767</v>
+        <v>-1.1558</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.1767</v>
+        <v>-1.1558</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.1767</v>
+        <v>-1.1558</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.1767</v>
+        <v>-1.1558</v>
       </c>
       <c r="N76" t="n">
         <v>299</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.3269</v>
+        <v>-1.3952</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7795</v>
+        <v>-0.8196</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2282</v>
+        <v>-1.237</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.3269</v>
+        <v>-1.3952</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.3269</v>
+        <v>-1.3404</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.3269</v>
+        <v>-1.3404</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.3269</v>
+        <v>-1.3404</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.3269</v>
+        <v>-1.3404</v>
       </c>
       <c r="N77" t="n">
         <v>188</v>
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.3491</v>
+        <v>-1.5265</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.7926</v>
+        <v>-0.8968</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2383</v>
+        <v>-1.2957</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.3491</v>
+        <v>-1.5265</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.3491</v>
+        <v>-1.3391</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.3491</v>
+        <v>-1.3391</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.3491</v>
+        <v>-1.3391</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.3491</v>
+        <v>-1.3391</v>
       </c>
       <c r="N78" t="n">
         <v>166</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.4781</v>
+        <v>-1.6893</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8683999999999999</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2971</v>
+        <v>-1.3684</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.4781</v>
+        <v>-1.6893</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.4781</v>
+        <v>-1.478</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.4781</v>
+        <v>-1.478</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.4781</v>
+        <v>-1.478</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.4781</v>
+        <v>-1.478</v>
       </c>
       <c r="N79" t="n">
         <v>178</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.2253</v>
+        <v>-2.6526</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.3073</v>
+        <v>-1.5583</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.6372</v>
+        <v>-1.7987</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.2253</v>
+        <v>-2.6526</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.7985</v>
+        <v>-1.7987</v>
       </c>
       <c r="G80" t="n">
-        <v>-0.4268</v>
+        <v>-0.4274</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.7985</v>
+        <v>-1.7987</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.8448</v>
+        <v>-1.8451</v>
       </c>
       <c r="J80" t="n">
-        <v>-0.4268</v>
+        <v>-0.4274</v>
       </c>
       <c r="K80" t="n">
         <v>236</v>
@@ -4117,7 +4117,7 @@
         <v>69</v>
       </c>
       <c r="M80" t="n">
-        <v>-2.2716</v>
+        <v>-2.2725</v>
       </c>
       <c r="N80" t="n">
         <v>305</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.4528</v>
+        <v>-2.8377</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.441</v>
+        <v>-1.6671</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.7408</v>
+        <v>-1.8814</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.4528</v>
+        <v>-2.8377</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.2998</v>
+        <v>-2.326</v>
       </c>
       <c r="G81" t="n">
         <v>-0.153</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.2998</v>
+        <v>-2.326</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.2998</v>
+        <v>-2.326</v>
       </c>
       <c r="J81" t="n">
         <v>-0.153</v>
@@ -4163,7 +4163,7 @@
         <v>77</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.4528</v>
+        <v>-2.479</v>
       </c>
       <c r="N81" t="n">
         <v>334</v>
@@ -4269,10 +4269,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2795</v>
+        <v>0.2807</v>
       </c>
       <c r="J2" t="n">
-        <v>6.149</v>
+        <v>6.1754</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.97</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0492</v>
+        <v>-0.0487</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0824</v>
+        <v>-1.0714</v>
       </c>
     </row>
     <row r="4">
@@ -4346,13 +4346,13 @@
         <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0638</v>
+        <v>-0.0772</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.4036</v>
+        <v>-1.6984</v>
       </c>
     </row>
     <row r="5">
@@ -4389,10 +4389,10 @@
         <v>0.8</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2414</v>
+        <v>-0.241</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.3108</v>
+        <v>-5.302</v>
       </c>
     </row>
     <row r="6">
@@ -4426,13 +4426,13 @@
         <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4356</v>
+        <v>-0.444</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.5832</v>
+        <v>-9.768000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -4466,13 +4466,13 @@
         <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4796</v>
+        <v>1.4943</v>
       </c>
       <c r="J7" t="n">
-        <v>32.5512</v>
+        <v>32.8746</v>
       </c>
     </row>
     <row r="8">
@@ -4509,10 +4509,10 @@
         <v>1.45</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0337</v>
+        <v>1.0328</v>
       </c>
       <c r="J8" t="n">
-        <v>22.7414</v>
+        <v>22.7216</v>
       </c>
     </row>
     <row r="9">
@@ -4546,13 +4546,13 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5399</v>
+        <v>0.5611</v>
       </c>
       <c r="J9" t="n">
-        <v>11.8778</v>
+        <v>12.3442</v>
       </c>
     </row>
     <row r="10">
@@ -4589,10 +4589,10 @@
         <v>1.12</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3535</v>
+        <v>0.3529</v>
       </c>
       <c r="J10" t="n">
-        <v>7.777</v>
+        <v>7.7638</v>
       </c>
     </row>
     <row r="11">
@@ -4629,10 +4629,10 @@
         <v>0.77</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7009</v>
+        <v>-0.7015</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.4198</v>
+        <v>-15.433</v>
       </c>
     </row>
     <row r="12">
@@ -4669,10 +4669,10 @@
         <v>1.12</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3205</v>
+        <v>0.3199</v>
       </c>
       <c r="J12" t="n">
-        <v>5.4485</v>
+        <v>5.4383</v>
       </c>
     </row>
     <row r="13">
@@ -4709,10 +4709,10 @@
         <v>1.03</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1226</v>
+        <v>0.1221</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0842</v>
+        <v>2.0757</v>
       </c>
     </row>
     <row r="14">
@@ -4746,13 +4746,13 @@
         <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0193</v>
+        <v>0.0634</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3281</v>
+        <v>1.0778</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.75</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2893</v>
+        <v>-0.2895</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.9181</v>
+        <v>-4.9215</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.5</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5133</v>
+        <v>-0.5135</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.726100000000001</v>
+        <v>-8.7295</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.68</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4142</v>
+        <v>1.4147</v>
       </c>
       <c r="J17" t="n">
-        <v>24.0414</v>
+        <v>24.0499</v>
       </c>
     </row>
     <row r="18">
@@ -4906,13 +4906,13 @@
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4142</v>
+        <v>1.3979</v>
       </c>
       <c r="J18" t="n">
-        <v>24.0414</v>
+        <v>23.7643</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.3</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7318</v>
+        <v>0.7321</v>
       </c>
       <c r="J19" t="n">
-        <v>12.4406</v>
+        <v>12.4457</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2569</v>
+        <v>0.2572</v>
       </c>
       <c r="J20" t="n">
-        <v>4.3673</v>
+        <v>4.3724</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>1.08</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2296</v>
+        <v>0.23</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9032</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.49</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9293</v>
+        <v>0.9283</v>
       </c>
       <c r="J22" t="n">
-        <v>16.7274</v>
+        <v>16.7094</v>
       </c>
     </row>
     <row r="23">
@@ -5106,13 +5106,13 @@
         <v>18</v>
       </c>
       <c r="H23" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0345</v>
+        <v>-0.0167</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.621</v>
+        <v>-0.3006</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>0.93</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1042</v>
+        <v>-0.1044</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8756</v>
+        <v>-1.8792</v>
       </c>
     </row>
     <row r="25">
@@ -5189,10 +5189,10 @@
         <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3376</v>
+        <v>-0.3378</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.0768</v>
+        <v>-6.0804</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>0.37</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6237</v>
+        <v>-0.6238</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.2266</v>
+        <v>-11.2284</v>
       </c>
     </row>
     <row r="27">
@@ -5466,13 +5466,13 @@
         <v>17</v>
       </c>
       <c r="H32" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5203</v>
+        <v>1.5009</v>
       </c>
       <c r="J32" t="n">
-        <v>25.8451</v>
+        <v>25.5153</v>
       </c>
     </row>
     <row r="33">
@@ -5506,13 +5506,13 @@
         <v>17</v>
       </c>
       <c r="H33" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3646</v>
+        <v>1.3074</v>
       </c>
       <c r="J33" t="n">
-        <v>23.1982</v>
+        <v>22.2258</v>
       </c>
     </row>
     <row r="34">
@@ -5546,13 +5546,13 @@
         <v>17</v>
       </c>
       <c r="H34" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4458</v>
+        <v>0.428</v>
       </c>
       <c r="J34" t="n">
-        <v>7.5786</v>
+        <v>7.276</v>
       </c>
     </row>
     <row r="35">
@@ -5586,13 +5586,13 @@
         <v>17</v>
       </c>
       <c r="H35" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.0056</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-1.0659</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.97</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2032</v>
+        <v>-0.2006</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.4544</v>
+        <v>-3.4102</v>
       </c>
     </row>
     <row r="37">
@@ -5666,13 +5666,13 @@
         <v>17</v>
       </c>
       <c r="H37" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1064</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.8088</v>
+        <v>-1.4127</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>0.82</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2075</v>
+        <v>-0.209</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.5275</v>
+        <v>-3.553</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.8</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2279</v>
+        <v>-0.2292</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.8743</v>
+        <v>-3.8964</v>
       </c>
     </row>
     <row r="40">
@@ -5786,13 +5786,13 @@
         <v>17</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3206</v>
+        <v>-0.3126</v>
       </c>
       <c r="J40" t="n">
-        <v>-5.4502</v>
+        <v>-5.3142</v>
       </c>
     </row>
     <row r="41">
@@ -5826,13 +5826,13 @@
         <v>17</v>
       </c>
       <c r="H41" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5419</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.212300000000001</v>
+        <v>-8.9369</v>
       </c>
     </row>
     <row r="42">
@@ -7269,10 +7269,10 @@
         <v>1.06</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1474</v>
+        <v>0.147</v>
       </c>
       <c r="J77" t="n">
-        <v>2.948</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="78">
@@ -7309,10 +7309,10 @@
         <v>1.02</v>
       </c>
       <c r="I78" t="n">
-        <v>0.0694</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>1.388</v>
+        <v>1.382</v>
       </c>
     </row>
     <row r="79">
@@ -7346,13 +7346,13 @@
         <v>20</v>
       </c>
       <c r="H79" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1507</v>
+        <v>-0.1398</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.014</v>
+        <v>-2.796</v>
       </c>
     </row>
     <row r="80">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1615</v>
+        <v>-0.1616</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.23</v>
+        <v>-3.232</v>
       </c>
     </row>
     <row r="81">
@@ -7429,10 +7429,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3482</v>
+        <v>-0.3484</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.964</v>
+        <v>-6.968</v>
       </c>
     </row>
     <row r="82">
@@ -8466,13 +8466,13 @@
         <v>19</v>
       </c>
       <c r="H107" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="I107" t="n">
-        <v>1.7869</v>
+        <v>1.7765</v>
       </c>
       <c r="J107" t="n">
-        <v>33.9511</v>
+        <v>33.7535</v>
       </c>
     </row>
     <row r="108">
@@ -8509,10 +8509,10 @@
         <v>1.41</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8122</v>
+        <v>0.8127</v>
       </c>
       <c r="J108" t="n">
-        <v>15.4318</v>
+        <v>15.4413</v>
       </c>
     </row>
     <row r="109">
@@ -8546,13 +8546,13 @@
         <v>19</v>
       </c>
       <c r="H109" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1168</v>
+        <v>0.0837</v>
       </c>
       <c r="J109" t="n">
-        <v>2.2192</v>
+        <v>1.5903</v>
       </c>
     </row>
     <row r="110">
@@ -8589,10 +8589,10 @@
         <v>1.01</v>
       </c>
       <c r="I110" t="n">
-        <v>0.0051</v>
+        <v>0.0058</v>
       </c>
       <c r="J110" t="n">
-        <v>0.0969</v>
+        <v>0.1102</v>
       </c>
     </row>
     <row r="111">
@@ -8629,10 +8629,10 @@
         <v>0.98</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.156</v>
+        <v>-0.1553</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.964</v>
+        <v>-2.9507</v>
       </c>
     </row>
     <row r="112">
@@ -9269,10 +9269,10 @@
         <v>1.14</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3393</v>
+        <v>0.3383</v>
       </c>
       <c r="J127" t="n">
-        <v>7.4646</v>
+        <v>7.4426</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.08</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2219</v>
+        <v>0.2211</v>
       </c>
       <c r="J128" t="n">
-        <v>4.8818</v>
+        <v>4.8642</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>0.98</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0399</v>
+        <v>-0.0402</v>
       </c>
       <c r="J129" t="n">
-        <v>-0.8778</v>
+        <v>-0.8844</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.97</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0554</v>
+        <v>-0.0557</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.2188</v>
+        <v>-1.2254</v>
       </c>
     </row>
     <row r="131">
@@ -9426,13 +9426,13 @@
         <v>22</v>
       </c>
       <c r="H131" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4505</v>
+        <v>-0.4333</v>
       </c>
       <c r="J131" t="n">
-        <v>-9.911</v>
+        <v>-9.5326</v>
       </c>
     </row>
     <row r="132">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3669</v>
+        <v>0.3662</v>
       </c>
       <c r="J147" t="n">
-        <v>7.7049</v>
+        <v>7.6902</v>
       </c>
     </row>
     <row r="148">
@@ -10109,10 +10109,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.288</v>
+        <v>0.2874</v>
       </c>
       <c r="J148" t="n">
-        <v>6.048</v>
+        <v>6.0354</v>
       </c>
     </row>
     <row r="149">
@@ -10146,13 +10146,13 @@
         <v>21</v>
       </c>
       <c r="H149" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1126</v>
+        <v>-0.1006</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.3646</v>
+        <v>-2.1126</v>
       </c>
     </row>
     <row r="150">
@@ -10189,10 +10189,10 @@
         <v>0.65</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3793</v>
+        <v>-0.3795</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.9653</v>
+        <v>-7.9695</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.47</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.5369</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.2728</v>
+        <v>-11.2749</v>
       </c>
     </row>
     <row r="152">
@@ -10466,13 +10466,13 @@
         <v>24</v>
       </c>
       <c r="H157" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8787</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>21.0888</v>
+        <v>20.8416</v>
       </c>
     </row>
     <row r="158">
@@ -10546,13 +10546,13 @@
         <v>24</v>
       </c>
       <c r="H159" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1709</v>
+        <v>-0.1598</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.1016</v>
+        <v>-3.8352</v>
       </c>
     </row>
     <row r="160">
@@ -15466,13 +15466,13 @@
         <v>30</v>
       </c>
       <c r="H282" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I282" t="n">
-        <v>1.3522</v>
+        <v>1.3643</v>
       </c>
       <c r="J282" t="n">
-        <v>40.566</v>
+        <v>40.929</v>
       </c>
     </row>
     <row r="283">
@@ -15506,13 +15506,13 @@
         <v>30</v>
       </c>
       <c r="H283" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1926</v>
+        <v>0.2212</v>
       </c>
       <c r="J283" t="n">
-        <v>5.778</v>
+        <v>6.636</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.01</v>
       </c>
       <c r="I284" t="n">
-        <v>0.0518</v>
+        <v>0.0512</v>
       </c>
       <c r="J284" t="n">
-        <v>1.554</v>
+        <v>1.536</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>0.8</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5986</v>
+        <v>-0.5994</v>
       </c>
       <c r="J285" t="n">
-        <v>-17.958</v>
+        <v>-17.982</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>0.76</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6892</v>
+        <v>-0.6899</v>
       </c>
       <c r="J286" t="n">
-        <v>-20.676</v>
+        <v>-20.697</v>
       </c>
     </row>
     <row r="287">
@@ -16866,13 +16866,13 @@
         <v>19</v>
       </c>
       <c r="H317" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="I317" t="n">
-        <v>1.769</v>
+        <v>1.7576</v>
       </c>
       <c r="J317" t="n">
-        <v>33.611</v>
+        <v>33.3944</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.34</v>
       </c>
       <c r="I318" t="n">
-        <v>0.8172</v>
+        <v>0.8175</v>
       </c>
       <c r="J318" t="n">
-        <v>15.5268</v>
+        <v>15.5325</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>1.16</v>
       </c>
       <c r="I319" t="n">
-        <v>0.4437</v>
+        <v>0.444</v>
       </c>
       <c r="J319" t="n">
-        <v>8.430300000000001</v>
+        <v>8.436</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>1.15</v>
       </c>
       <c r="I320" t="n">
-        <v>0.4202</v>
+        <v>0.4205</v>
       </c>
       <c r="J320" t="n">
-        <v>7.9838</v>
+        <v>7.9895</v>
       </c>
     </row>
     <row r="321">
@@ -17029,10 +17029,10 @@
         <v>0.75</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7509</v>
+        <v>-0.7506</v>
       </c>
       <c r="J321" t="n">
-        <v>-14.2671</v>
+        <v>-14.2614</v>
       </c>
     </row>
     <row r="322">
@@ -18269,10 +18269,10 @@
         <v>2.13</v>
       </c>
       <c r="I352" t="n">
-        <v>1.8288</v>
+        <v>1.8293</v>
       </c>
       <c r="J352" t="n">
-        <v>31.0896</v>
+        <v>31.0981</v>
       </c>
     </row>
     <row r="353">
@@ -18309,10 +18309,10 @@
         <v>1.62</v>
       </c>
       <c r="I353" t="n">
-        <v>1.2189</v>
+        <v>1.2191</v>
       </c>
       <c r="J353" t="n">
-        <v>20.7213</v>
+        <v>20.7247</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>1.61</v>
       </c>
       <c r="I354" t="n">
-        <v>1.2063</v>
+        <v>1.2066</v>
       </c>
       <c r="J354" t="n">
-        <v>20.5071</v>
+        <v>20.5122</v>
       </c>
     </row>
     <row r="355">
@@ -18386,13 +18386,13 @@
         <v>17</v>
       </c>
       <c r="H355" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I355" t="n">
-        <v>0.2706</v>
+        <v>0.2443</v>
       </c>
       <c r="J355" t="n">
-        <v>4.6002</v>
+        <v>4.1531</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.8</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.6617</v>
+        <v>-0.6615</v>
       </c>
       <c r="J356" t="n">
-        <v>-11.2489</v>
+        <v>-11.2455</v>
       </c>
     </row>
     <row r="357">
@@ -18466,13 +18466,13 @@
         <v>17</v>
       </c>
       <c r="H357" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I357" t="n">
-        <v>0.3019</v>
+        <v>0.3223</v>
       </c>
       <c r="J357" t="n">
-        <v>5.1323</v>
+        <v>5.4791</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>0.92</v>
       </c>
       <c r="I358" t="n">
-        <v>-0.0993</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J358" t="n">
-        <v>-1.6881</v>
+        <v>-1.6932</v>
       </c>
     </row>
     <row r="359">
@@ -18549,10 +18549,10 @@
         <v>0.7</v>
       </c>
       <c r="I359" t="n">
-        <v>-0.3236</v>
+        <v>-0.3238</v>
       </c>
       <c r="J359" t="n">
-        <v>-5.5012</v>
+        <v>-5.5046</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>0.59</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.4226</v>
+        <v>-0.4229</v>
       </c>
       <c r="J360" t="n">
-        <v>-7.1842</v>
+        <v>-7.1893</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.52</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4842</v>
+        <v>-0.4845</v>
       </c>
       <c r="J361" t="n">
-        <v>-8.231400000000001</v>
+        <v>-8.236499999999999</v>
       </c>
     </row>
     <row r="362">
@@ -18666,13 +18666,13 @@
         <v>18</v>
       </c>
       <c r="H362" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I362" t="n">
-        <v>0.9116</v>
+        <v>0.903</v>
       </c>
       <c r="J362" t="n">
-        <v>16.4088</v>
+        <v>16.254</v>
       </c>
     </row>
     <row r="363">
@@ -18709,10 +18709,10 @@
         <v>1.83</v>
       </c>
       <c r="I363" t="n">
-        <v>0.9028</v>
+        <v>0.903</v>
       </c>
       <c r="J363" t="n">
-        <v>16.2504</v>
+        <v>16.254</v>
       </c>
     </row>
     <row r="364">
@@ -18749,10 +18749,10 @@
         <v>1.7</v>
       </c>
       <c r="I364" t="n">
-        <v>0.7852</v>
+        <v>0.7854</v>
       </c>
       <c r="J364" t="n">
-        <v>14.1336</v>
+        <v>14.1372</v>
       </c>
     </row>
     <row r="365">
@@ -18789,10 +18789,10 @@
         <v>1.01</v>
       </c>
       <c r="I365" t="n">
-        <v>-0.0053</v>
+        <v>-0.0052</v>
       </c>
       <c r="J365" t="n">
-        <v>-0.0954</v>
+        <v>-0.0936</v>
       </c>
     </row>
     <row r="366">
@@ -18829,10 +18829,10 @@
         <v>0.83</v>
       </c>
       <c r="I366" t="n">
-        <v>-0.254</v>
+        <v>-0.2539</v>
       </c>
       <c r="J366" t="n">
-        <v>-4.572</v>
+        <v>-4.5702</v>
       </c>
     </row>
     <row r="367">
@@ -20269,10 +20269,10 @@
         <v>1.58</v>
       </c>
       <c r="I402" t="n">
-        <v>1.2128</v>
+        <v>1.2133</v>
       </c>
       <c r="J402" t="n">
-        <v>24.256</v>
+        <v>24.266</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.45</v>
       </c>
       <c r="I403" t="n">
-        <v>1.0327</v>
+        <v>1.0331</v>
       </c>
       <c r="J403" t="n">
-        <v>20.654</v>
+        <v>20.662</v>
       </c>
     </row>
     <row r="404">
@@ -20346,13 +20346,13 @@
         <v>20</v>
       </c>
       <c r="H404" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I404" t="n">
-        <v>0.502</v>
+        <v>0.4798</v>
       </c>
       <c r="J404" t="n">
-        <v>10.04</v>
+        <v>9.596</v>
       </c>
     </row>
     <row r="405">
@@ -20389,10 +20389,10 @@
         <v>1.01</v>
       </c>
       <c r="I405" t="n">
-        <v>0.0262</v>
+        <v>0.0266</v>
       </c>
       <c r="J405" t="n">
-        <v>0.524</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="406">
@@ -20429,10 +20429,10 @@
         <v>0.78</v>
       </c>
       <c r="I406" t="n">
-        <v>-0.6708</v>
+        <v>-0.6705</v>
       </c>
       <c r="J406" t="n">
-        <v>-13.416</v>
+        <v>-13.41</v>
       </c>
     </row>
     <row r="407">
@@ -20869,10 +20869,10 @@
         <v>1.24</v>
       </c>
       <c r="I417" t="n">
-        <v>0.5201</v>
+        <v>0.5194</v>
       </c>
       <c r="J417" t="n">
-        <v>11.4422</v>
+        <v>11.4268</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.09</v>
       </c>
       <c r="I418" t="n">
-        <v>0.2466</v>
+        <v>0.2461</v>
       </c>
       <c r="J418" t="n">
-        <v>5.4252</v>
+        <v>5.4142</v>
       </c>
     </row>
     <row r="419">
@@ -20949,10 +20949,10 @@
         <v>0.82</v>
       </c>
       <c r="I419" t="n">
-        <v>-0.2261</v>
+        <v>-0.2263</v>
       </c>
       <c r="J419" t="n">
-        <v>-4.9742</v>
+        <v>-4.9786</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.79</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.2559</v>
+        <v>-0.2561</v>
       </c>
       <c r="J420" t="n">
-        <v>-5.6298</v>
+        <v>-5.6342</v>
       </c>
     </row>
     <row r="421">
@@ -21026,13 +21026,13 @@
         <v>22</v>
       </c>
       <c r="H421" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.3228</v>
+        <v>-0.3136</v>
       </c>
       <c r="J421" t="n">
-        <v>-7.1016</v>
+        <v>-6.8992</v>
       </c>
     </row>
     <row r="422">
@@ -23109,10 +23109,10 @@
         <v>1.3</v>
       </c>
       <c r="I473" t="n">
-        <v>0.7343</v>
+        <v>0.7346</v>
       </c>
       <c r="J473" t="n">
-        <v>14.686</v>
+        <v>14.692</v>
       </c>
     </row>
     <row r="474">
@@ -23146,13 +23146,13 @@
         <v>20</v>
       </c>
       <c r="H474" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I474" t="n">
-        <v>0.3125</v>
+        <v>0.2869</v>
       </c>
       <c r="J474" t="n">
-        <v>6.25</v>
+        <v>5.738</v>
       </c>
     </row>
     <row r="475">
@@ -23189,10 +23189,10 @@
         <v>0.98</v>
       </c>
       <c r="I475" t="n">
-        <v>-0.1591</v>
+        <v>-0.1588</v>
       </c>
       <c r="J475" t="n">
-        <v>-3.182</v>
+        <v>-3.176</v>
       </c>
     </row>
     <row r="476">
@@ -23229,10 +23229,10 @@
         <v>0.96</v>
       </c>
       <c r="I476" t="n">
-        <v>-0.2295</v>
+        <v>-0.2292</v>
       </c>
       <c r="J476" t="n">
-        <v>-4.59</v>
+        <v>-4.584</v>
       </c>
     </row>
     <row r="477">
@@ -25069,10 +25069,10 @@
         <v>1.85</v>
       </c>
       <c r="I522" t="n">
-        <v>1.5226</v>
+        <v>1.523</v>
       </c>
       <c r="J522" t="n">
-        <v>27.4068</v>
+        <v>27.414</v>
       </c>
     </row>
     <row r="523">
@@ -25109,10 +25109,10 @@
         <v>1.6</v>
       </c>
       <c r="I523" t="n">
-        <v>1.209</v>
+        <v>1.2093</v>
       </c>
       <c r="J523" t="n">
-        <v>21.762</v>
+        <v>21.7674</v>
       </c>
     </row>
     <row r="524">
@@ -25146,13 +25146,13 @@
         <v>18</v>
       </c>
       <c r="H524" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I524" t="n">
-        <v>0.7922</v>
+        <v>0.7733</v>
       </c>
       <c r="J524" t="n">
-        <v>14.2596</v>
+        <v>13.9194</v>
       </c>
     </row>
     <row r="525">
@@ -25189,10 +25189,10 @@
         <v>1.11</v>
       </c>
       <c r="I525" t="n">
-        <v>0.3122</v>
+        <v>0.3125</v>
       </c>
       <c r="J525" t="n">
-        <v>5.6196</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="526">
@@ -25229,10 +25229,10 @@
         <v>0.85</v>
       </c>
       <c r="I526" t="n">
-        <v>-0.5306</v>
+        <v>-0.5303</v>
       </c>
       <c r="J526" t="n">
-        <v>-9.550800000000001</v>
+        <v>-9.545400000000001</v>
       </c>
     </row>
     <row r="527">
@@ -25869,10 +25869,10 @@
         <v>1.77</v>
       </c>
       <c r="I542" t="n">
-        <v>1.4617</v>
+        <v>1.4611</v>
       </c>
       <c r="J542" t="n">
-        <v>49.6978</v>
+        <v>49.6774</v>
       </c>
     </row>
     <row r="543">
@@ -25909,10 +25909,10 @@
         <v>1.44</v>
       </c>
       <c r="I543" t="n">
-        <v>1.0171</v>
+        <v>1.0167</v>
       </c>
       <c r="J543" t="n">
-        <v>34.5814</v>
+        <v>34.5678</v>
       </c>
     </row>
     <row r="544">
@@ -25946,13 +25946,13 @@
         <v>34</v>
       </c>
       <c r="H544" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I544" t="n">
-        <v>0.5452</v>
+        <v>0.5661</v>
       </c>
       <c r="J544" t="n">
-        <v>18.5368</v>
+        <v>19.2474</v>
       </c>
     </row>
     <row r="545">
@@ -25989,10 +25989,10 @@
         <v>0.93</v>
       </c>
       <c r="I545" t="n">
-        <v>-0.2971</v>
+        <v>-0.2975</v>
       </c>
       <c r="J545" t="n">
-        <v>-10.1014</v>
+        <v>-10.115</v>
       </c>
     </row>
     <row r="546">
@@ -26029,10 +26029,10 @@
         <v>0.66</v>
       </c>
       <c r="I546" t="n">
-        <v>-0.9284</v>
+        <v>-0.9287</v>
       </c>
       <c r="J546" t="n">
-        <v>-31.5656</v>
+        <v>-31.5758</v>
       </c>
     </row>
     <row r="547">
@@ -27669,10 +27669,10 @@
         <v>2.11</v>
       </c>
       <c r="I587" t="n">
-        <v>1.7725</v>
+        <v>1.7729</v>
       </c>
       <c r="J587" t="n">
-        <v>26.5875</v>
+        <v>26.5935</v>
       </c>
     </row>
     <row r="588">
@@ -27706,13 +27706,13 @@
         <v>15</v>
       </c>
       <c r="H588" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="I588" t="n">
-        <v>1.5453</v>
+        <v>1.534</v>
       </c>
       <c r="J588" t="n">
-        <v>23.1795</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="589">
@@ -27749,10 +27749,10 @@
         <v>1.62</v>
       </c>
       <c r="I589" t="n">
-        <v>1.2035</v>
+        <v>1.2036</v>
       </c>
       <c r="J589" t="n">
-        <v>18.0525</v>
+        <v>18.054</v>
       </c>
     </row>
     <row r="590">
@@ -27789,10 +27789,10 @@
         <v>1.28</v>
       </c>
       <c r="I590" t="n">
-        <v>0.6579</v>
+        <v>0.6581</v>
       </c>
       <c r="J590" t="n">
-        <v>9.868499999999999</v>
+        <v>9.871499999999999</v>
       </c>
     </row>
     <row r="591">
@@ -27829,10 +27829,10 @@
         <v>1.14</v>
       </c>
       <c r="I591" t="n">
-        <v>0.3492</v>
+        <v>0.3495</v>
       </c>
       <c r="J591" t="n">
-        <v>5.238</v>
+        <v>5.2425</v>
       </c>
     </row>
     <row r="592">
@@ -28469,10 +28469,10 @@
         <v>1.33</v>
       </c>
       <c r="I607" t="n">
-        <v>0.6653</v>
+        <v>0.666</v>
       </c>
       <c r="J607" t="n">
-        <v>13.9713</v>
+        <v>13.986</v>
       </c>
     </row>
     <row r="608">
@@ -28506,13 +28506,13 @@
         <v>21</v>
       </c>
       <c r="H608" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I608" t="n">
-        <v>-0.0544</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="J608" t="n">
-        <v>-1.1424</v>
+        <v>-1.4406</v>
       </c>
     </row>
     <row r="609">
@@ -28549,10 +28549,10 @@
         <v>0.88</v>
       </c>
       <c r="I609" t="n">
-        <v>-0.1637</v>
+        <v>-0.1636</v>
       </c>
       <c r="J609" t="n">
-        <v>-3.4377</v>
+        <v>-3.4356</v>
       </c>
     </row>
     <row r="610">
@@ -28589,10 +28589,10 @@
         <v>0.76</v>
       </c>
       <c r="I610" t="n">
-        <v>-0.2854</v>
+        <v>-0.2852</v>
       </c>
       <c r="J610" t="n">
-        <v>-5.9934</v>
+        <v>-5.9892</v>
       </c>
     </row>
     <row r="611">
@@ -28629,10 +28629,10 @@
         <v>0.74</v>
       </c>
       <c r="I611" t="n">
-        <v>-0.3044</v>
+        <v>-0.3042</v>
       </c>
       <c r="J611" t="n">
-        <v>-6.3924</v>
+        <v>-6.3882</v>
       </c>
     </row>
     <row r="612">
@@ -29869,10 +29869,10 @@
         <v>1.54</v>
       </c>
       <c r="I642" t="n">
-        <v>1.1344</v>
+        <v>1.1347</v>
       </c>
       <c r="J642" t="n">
-        <v>22.688</v>
+        <v>22.694</v>
       </c>
     </row>
     <row r="643">
@@ -29906,13 +29906,13 @@
         <v>20</v>
       </c>
       <c r="H643" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I643" t="n">
-        <v>0.7752</v>
+        <v>0.7562</v>
       </c>
       <c r="J643" t="n">
-        <v>15.504</v>
+        <v>15.124</v>
       </c>
     </row>
     <row r="644">
@@ -29949,10 +29949,10 @@
         <v>1.31</v>
       </c>
       <c r="I644" t="n">
-        <v>0.756</v>
+        <v>0.7562</v>
       </c>
       <c r="J644" t="n">
-        <v>15.12</v>
+        <v>15.124</v>
       </c>
     </row>
     <row r="645">
@@ -29989,10 +29989,10 @@
         <v>1.3</v>
       </c>
       <c r="I645" t="n">
-        <v>0.7366</v>
+        <v>0.7368</v>
       </c>
       <c r="J645" t="n">
-        <v>14.732</v>
+        <v>14.736</v>
       </c>
     </row>
     <row r="646">
@@ -30029,10 +30029,10 @@
         <v>1.16</v>
       </c>
       <c r="I646" t="n">
-        <v>0.4378</v>
+        <v>0.4381</v>
       </c>
       <c r="J646" t="n">
-        <v>8.756</v>
+        <v>8.762</v>
       </c>
     </row>
     <row r="647">
@@ -30069,10 +30069,10 @@
         <v>1.32</v>
       </c>
       <c r="I647" t="n">
-        <v>0.6806</v>
+        <v>0.6788</v>
       </c>
       <c r="J647" t="n">
-        <v>13.612</v>
+        <v>13.576</v>
       </c>
     </row>
     <row r="648">
@@ -30106,13 +30106,13 @@
         <v>20</v>
       </c>
       <c r="H648" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="I648" t="n">
-        <v>-0.0607</v>
+        <v>-0.0464</v>
       </c>
       <c r="J648" t="n">
-        <v>-1.214</v>
+        <v>-0.928</v>
       </c>
     </row>
     <row r="649">
@@ -30149,10 +30149,10 @@
         <v>0.87</v>
       </c>
       <c r="I649" t="n">
-        <v>-0.169</v>
+        <v>-0.1693</v>
       </c>
       <c r="J649" t="n">
-        <v>-3.38</v>
+        <v>-3.386</v>
       </c>
     </row>
     <row r="650">
@@ -30186,13 +30186,13 @@
         <v>20</v>
       </c>
       <c r="H650" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="I650" t="n">
-        <v>-0.4153</v>
+        <v>-0.4068</v>
       </c>
       <c r="J650" t="n">
-        <v>-8.305999999999999</v>
+        <v>-8.135999999999999</v>
       </c>
     </row>
     <row r="651">
@@ -30229,10 +30229,10 @@
         <v>0.53</v>
       </c>
       <c r="I651" t="n">
-        <v>-0.4854</v>
+        <v>-0.4858</v>
       </c>
       <c r="J651" t="n">
-        <v>-9.708</v>
+        <v>-9.715999999999999</v>
       </c>
     </row>
     <row r="652">
@@ -30469,10 +30469,10 @@
         <v>1.06</v>
       </c>
       <c r="I657" t="n">
-        <v>0.2115</v>
+        <v>0.2122</v>
       </c>
       <c r="J657" t="n">
-        <v>4.23</v>
+        <v>4.244</v>
       </c>
     </row>
     <row r="658">
@@ -30509,10 +30509,10 @@
         <v>0.87</v>
       </c>
       <c r="I658" t="n">
-        <v>-0.1662</v>
+        <v>-0.166</v>
       </c>
       <c r="J658" t="n">
-        <v>-3.324</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="659">
@@ -30549,10 +30549,10 @@
         <v>0.77</v>
       </c>
       <c r="I659" t="n">
-        <v>-0.2648</v>
+        <v>-0.2646</v>
       </c>
       <c r="J659" t="n">
-        <v>-5.296</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="660">
@@ -30586,13 +30586,13 @@
         <v>20</v>
       </c>
       <c r="H660" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I660" t="n">
-        <v>-0.3026</v>
+        <v>-0.3117</v>
       </c>
       <c r="J660" t="n">
-        <v>-6.052</v>
+        <v>-6.234</v>
       </c>
     </row>
     <row r="661">
@@ -30629,10 +30629,10 @@
         <v>0.7</v>
       </c>
       <c r="I661" t="n">
-        <v>-0.3304</v>
+        <v>-0.3302</v>
       </c>
       <c r="J661" t="n">
-        <v>-6.608</v>
+        <v>-6.604</v>
       </c>
     </row>
     <row r="662">
@@ -31066,13 +31066,13 @@
         <v>22</v>
       </c>
       <c r="H672" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I672" t="n">
-        <v>0.8669</v>
+        <v>0.8847</v>
       </c>
       <c r="J672" t="n">
-        <v>19.0718</v>
+        <v>19.4634</v>
       </c>
     </row>
     <row r="673">
@@ -31109,10 +31109,10 @@
         <v>1.77</v>
       </c>
       <c r="I673" t="n">
-        <v>0.8669</v>
+        <v>0.8663</v>
       </c>
       <c r="J673" t="n">
-        <v>19.0718</v>
+        <v>19.0586</v>
       </c>
     </row>
     <row r="674">
@@ -31149,10 +31149,10 @@
         <v>1.28</v>
       </c>
       <c r="I674" t="n">
-        <v>0.3828</v>
+        <v>0.3825</v>
       </c>
       <c r="J674" t="n">
-        <v>8.4216</v>
+        <v>8.414999999999999</v>
       </c>
     </row>
     <row r="675">
@@ -31189,10 +31189,10 @@
         <v>1.06</v>
       </c>
       <c r="I675" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.0982</v>
       </c>
       <c r="J675" t="n">
-        <v>2.1692</v>
+        <v>2.1604</v>
       </c>
     </row>
     <row r="676">
@@ -31229,10 +31229,10 @@
         <v>0.72</v>
       </c>
       <c r="I676" t="n">
-        <v>-0.3523</v>
+        <v>-0.3526</v>
       </c>
       <c r="J676" t="n">
-        <v>-7.7506</v>
+        <v>-7.7572</v>
       </c>
     </row>
     <row r="677">
@@ -32069,10 +32069,10 @@
         <v>1.63</v>
       </c>
       <c r="I697" t="n">
-        <v>1.3016</v>
+        <v>1.3022</v>
       </c>
       <c r="J697" t="n">
-        <v>29.9368</v>
+        <v>29.9506</v>
       </c>
     </row>
     <row r="698">
@@ -32109,10 +32109,10 @@
         <v>1.3</v>
       </c>
       <c r="I698" t="n">
-        <v>0.7704</v>
+        <v>0.771</v>
       </c>
       <c r="J698" t="n">
-        <v>17.7192</v>
+        <v>17.733</v>
       </c>
     </row>
     <row r="699">
@@ -32149,10 +32149,10 @@
         <v>1.06</v>
       </c>
       <c r="I699" t="n">
-        <v>0.2127</v>
+        <v>0.213</v>
       </c>
       <c r="J699" t="n">
-        <v>4.8921</v>
+        <v>4.899</v>
       </c>
     </row>
     <row r="700">
@@ -32186,13 +32186,13 @@
         <v>23</v>
       </c>
       <c r="H700" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I700" t="n">
-        <v>0.0814</v>
+        <v>0.0404</v>
       </c>
       <c r="J700" t="n">
-        <v>1.8722</v>
+        <v>0.9292</v>
       </c>
     </row>
     <row r="701">
@@ -32229,10 +32229,10 @@
         <v>0.6</v>
       </c>
       <c r="I701" t="n">
-        <v>-1.0385</v>
+        <v>-1.0382</v>
       </c>
       <c r="J701" t="n">
-        <v>-23.8855</v>
+        <v>-23.8786</v>
       </c>
     </row>
     <row r="702">
@@ -33669,10 +33669,10 @@
         <v>1.49</v>
       </c>
       <c r="I737" t="n">
-        <v>0.6241</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="J737" t="n">
-        <v>14.3543</v>
+        <v>14.3635</v>
       </c>
     </row>
     <row r="738">
@@ -33706,13 +33706,13 @@
         <v>23</v>
       </c>
       <c r="H738" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I738" t="n">
-        <v>0.54</v>
+        <v>0.5296</v>
       </c>
       <c r="J738" t="n">
-        <v>12.42</v>
+        <v>12.1808</v>
       </c>
     </row>
     <row r="739">
@@ -33749,10 +33749,10 @@
         <v>1.17</v>
       </c>
       <c r="I739" t="n">
-        <v>0.2662</v>
+        <v>0.2663</v>
       </c>
       <c r="J739" t="n">
-        <v>6.1226</v>
+        <v>6.1249</v>
       </c>
     </row>
     <row r="740">
@@ -33789,10 +33789,10 @@
         <v>0.98</v>
       </c>
       <c r="I740" t="n">
-        <v>-0.0538</v>
+        <v>-0.0536</v>
       </c>
       <c r="J740" t="n">
-        <v>-1.2374</v>
+        <v>-1.2328</v>
       </c>
     </row>
     <row r="741">
@@ -33829,10 +33829,10 @@
         <v>0.68</v>
       </c>
       <c r="I741" t="n">
-        <v>-0.3774</v>
+        <v>-0.3773</v>
       </c>
       <c r="J741" t="n">
-        <v>-8.680199999999999</v>
+        <v>-8.677899999999999</v>
       </c>
     </row>
     <row r="742">
@@ -35109,10 +35109,10 @@
         <v>1.14</v>
       </c>
       <c r="I773" t="n">
-        <v>0.3922</v>
+        <v>0.3925</v>
       </c>
       <c r="J773" t="n">
-        <v>8.2362</v>
+        <v>8.2425</v>
       </c>
     </row>
     <row r="774">
@@ -35146,13 +35146,13 @@
         <v>21</v>
       </c>
       <c r="H774" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="I774" t="n">
-        <v>0.3176</v>
+        <v>0.292</v>
       </c>
       <c r="J774" t="n">
-        <v>6.6696</v>
+        <v>6.132</v>
       </c>
     </row>
     <row r="775">
@@ -35189,10 +35189,10 @@
         <v>1</v>
       </c>
       <c r="I775" t="n">
-        <v>-0.0528</v>
+        <v>-0.0524</v>
       </c>
       <c r="J775" t="n">
-        <v>-1.1088</v>
+        <v>-1.1004</v>
       </c>
     </row>
     <row r="776">
@@ -35229,10 +35229,10 @@
         <v>0.93</v>
       </c>
       <c r="I776" t="n">
-        <v>-0.3161</v>
+        <v>-0.3158</v>
       </c>
       <c r="J776" t="n">
-        <v>-6.6381</v>
+        <v>-6.6318</v>
       </c>
     </row>
     <row r="777">
@@ -35669,10 +35669,10 @@
         <v>1.44</v>
       </c>
       <c r="I787" t="n">
-        <v>0.8136</v>
+        <v>0.8143</v>
       </c>
       <c r="J787" t="n">
-        <v>24.408</v>
+        <v>24.429</v>
       </c>
     </row>
     <row r="788">
@@ -35709,10 +35709,10 @@
         <v>1.23</v>
       </c>
       <c r="I788" t="n">
-        <v>0.4862</v>
+        <v>0.4867</v>
       </c>
       <c r="J788" t="n">
-        <v>14.586</v>
+        <v>14.601</v>
       </c>
     </row>
     <row r="789">
@@ -35746,13 +35746,13 @@
         <v>30</v>
       </c>
       <c r="H789" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I789" t="n">
-        <v>-0.1795</v>
+        <v>-0.19</v>
       </c>
       <c r="J789" t="n">
-        <v>-5.385</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="790">
@@ -35789,10 +35789,10 @@
         <v>0.71</v>
       </c>
       <c r="I790" t="n">
-        <v>-0.3377</v>
+        <v>-0.3376</v>
       </c>
       <c r="J790" t="n">
-        <v>-10.131</v>
+        <v>-10.128</v>
       </c>
     </row>
     <row r="791">
@@ -35829,10 +35829,10 @@
         <v>0.71</v>
       </c>
       <c r="I791" t="n">
-        <v>-0.3377</v>
+        <v>-0.3376</v>
       </c>
       <c r="J791" t="n">
-        <v>-10.131</v>
+        <v>-10.128</v>
       </c>
     </row>
     <row r="792">
@@ -35869,10 +35869,10 @@
         <v>1.26</v>
       </c>
       <c r="I792" t="n">
-        <v>0.4462</v>
+        <v>0.4468</v>
       </c>
       <c r="J792" t="n">
-        <v>9.8164</v>
+        <v>9.829599999999999</v>
       </c>
     </row>
     <row r="793">
@@ -35909,10 +35909,10 @@
         <v>1</v>
       </c>
       <c r="I793" t="n">
-        <v>0.014</v>
+        <v>0.0144</v>
       </c>
       <c r="J793" t="n">
-        <v>0.308</v>
+        <v>0.3168</v>
       </c>
     </row>
     <row r="794">
@@ -35949,10 +35949,10 @@
         <v>0.98</v>
       </c>
       <c r="I794" t="n">
-        <v>-0.0335</v>
+        <v>-0.0333</v>
       </c>
       <c r="J794" t="n">
-        <v>-0.737</v>
+        <v>-0.7326</v>
       </c>
     </row>
     <row r="795">
@@ -35986,13 +35986,13 @@
         <v>22</v>
       </c>
       <c r="H795" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="I795" t="n">
-        <v>-0.2514</v>
+        <v>-0.261</v>
       </c>
       <c r="J795" t="n">
-        <v>-5.5308</v>
+        <v>-5.742</v>
       </c>
     </row>
     <row r="796">
@@ -36029,10 +36029,10 @@
         <v>0.4</v>
       </c>
       <c r="I796" t="n">
-        <v>-0.5982</v>
+        <v>-0.598</v>
       </c>
       <c r="J796" t="n">
-        <v>-13.1604</v>
+        <v>-13.156</v>
       </c>
     </row>
     <row r="797">
@@ -36069,10 +36069,10 @@
         <v>1.83</v>
       </c>
       <c r="I797" t="n">
-        <v>0.948</v>
+        <v>0.9475</v>
       </c>
       <c r="J797" t="n">
-        <v>20.856</v>
+        <v>20.845</v>
       </c>
     </row>
     <row r="798">
@@ -36109,10 +36109,10 @@
         <v>1.4</v>
       </c>
       <c r="I798" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5224</v>
       </c>
       <c r="J798" t="n">
-        <v>11.4994</v>
+        <v>11.4928</v>
       </c>
     </row>
     <row r="799">
@@ -36146,13 +36146,13 @@
         <v>22</v>
       </c>
       <c r="H799" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I799" t="n">
-        <v>0.276</v>
+        <v>0.2878</v>
       </c>
       <c r="J799" t="n">
-        <v>6.072</v>
+        <v>6.3316</v>
       </c>
     </row>
     <row r="800">
@@ -36189,10 +36189,10 @@
         <v>0.79</v>
       </c>
       <c r="I800" t="n">
-        <v>-0.2778</v>
+        <v>-0.278</v>
       </c>
       <c r="J800" t="n">
-        <v>-6.1116</v>
+        <v>-6.116</v>
       </c>
     </row>
     <row r="801">
@@ -36229,10 +36229,10 @@
         <v>0.75</v>
       </c>
       <c r="I801" t="n">
-        <v>-0.3162</v>
+        <v>-0.3163</v>
       </c>
       <c r="J801" t="n">
-        <v>-6.9564</v>
+        <v>-6.9586</v>
       </c>
     </row>
     <row r="802">
@@ -36478,7 +36478,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
@@ -36518,7 +36518,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
@@ -36669,10 +36669,10 @@
         <v>1.78</v>
       </c>
       <c r="I812" t="n">
-        <v>1.4306</v>
+        <v>1.4301</v>
       </c>
       <c r="J812" t="n">
-        <v>25.7508</v>
+        <v>25.7418</v>
       </c>
     </row>
     <row r="813">
@@ -36709,10 +36709,10 @@
         <v>1.63</v>
       </c>
       <c r="I813" t="n">
-        <v>1.2428</v>
+        <v>1.2424</v>
       </c>
       <c r="J813" t="n">
-        <v>22.3704</v>
+        <v>22.3632</v>
       </c>
     </row>
     <row r="814">
@@ -36746,13 +36746,13 @@
         <v>18</v>
       </c>
       <c r="H814" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I814" t="n">
-        <v>0.8083</v>
+        <v>0.827</v>
       </c>
       <c r="J814" t="n">
-        <v>14.5494</v>
+        <v>14.886</v>
       </c>
     </row>
     <row r="815">
@@ -36789,10 +36789,10 @@
         <v>1.13</v>
       </c>
       <c r="I815" t="n">
-        <v>0.3581</v>
+        <v>0.3578</v>
       </c>
       <c r="J815" t="n">
-        <v>6.4458</v>
+        <v>6.4404</v>
       </c>
     </row>
     <row r="816">
@@ -36829,10 +36829,10 @@
         <v>1</v>
       </c>
       <c r="I816" t="n">
-        <v>-0.0624</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="J816" t="n">
-        <v>-1.1232</v>
+        <v>-1.1286</v>
       </c>
     </row>
     <row r="817">
@@ -37469,10 +37469,10 @@
         <v>1.34</v>
       </c>
       <c r="I832" t="n">
-        <v>0.8408</v>
+        <v>0.8403</v>
       </c>
       <c r="J832" t="n">
-        <v>18.4976</v>
+        <v>18.4866</v>
       </c>
     </row>
     <row r="833">
@@ -37506,13 +37506,13 @@
         <v>22</v>
       </c>
       <c r="H833" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="I833" t="n">
-        <v>0.5923</v>
+        <v>0.5704</v>
       </c>
       <c r="J833" t="n">
-        <v>13.0306</v>
+        <v>12.5488</v>
       </c>
     </row>
     <row r="834">
@@ -37546,13 +37546,13 @@
         <v>22</v>
       </c>
       <c r="H834" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I834" t="n">
-        <v>0.5051</v>
+        <v>0.5268</v>
       </c>
       <c r="J834" t="n">
-        <v>11.1122</v>
+        <v>11.5896</v>
       </c>
     </row>
     <row r="835">
@@ -37589,10 +37589,10 @@
         <v>1.12</v>
       </c>
       <c r="I835" t="n">
-        <v>0.3663</v>
+        <v>0.366</v>
       </c>
       <c r="J835" t="n">
-        <v>8.0586</v>
+        <v>8.052</v>
       </c>
     </row>
     <row r="836">
@@ -37626,13 +37626,13 @@
         <v>22</v>
       </c>
       <c r="H836" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I836" t="n">
-        <v>-0.1654</v>
+        <v>-0.1292</v>
       </c>
       <c r="J836" t="n">
-        <v>-3.6388</v>
+        <v>-2.8424</v>
       </c>
     </row>
     <row r="837">
@@ -37946,13 +37946,13 @@
         <v>29</v>
       </c>
       <c r="H844" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="I844" t="n">
-        <v>-0.246</v>
+        <v>-0.2559</v>
       </c>
       <c r="J844" t="n">
-        <v>-7.134</v>
+        <v>-7.4211</v>
       </c>
     </row>
     <row r="845">
@@ -38026,13 +38026,13 @@
         <v>29</v>
       </c>
       <c r="H846" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="I846" t="n">
-        <v>-0.3506</v>
+        <v>-0.3414</v>
       </c>
       <c r="J846" t="n">
-        <v>-10.1674</v>
+        <v>-9.900600000000001</v>
       </c>
     </row>
     <row r="847">
@@ -38069,10 +38069,10 @@
         <v>1.4</v>
       </c>
       <c r="I847" t="n">
-        <v>0.5271</v>
+        <v>0.5268</v>
       </c>
       <c r="J847" t="n">
-        <v>15.2859</v>
+        <v>15.2772</v>
       </c>
     </row>
     <row r="848">
@@ -38109,16 +38109,16 @@
         <v>1.17</v>
       </c>
       <c r="I848" t="n">
-        <v>0.2653</v>
+        <v>0.2652</v>
       </c>
       <c r="J848" t="n">
-        <v>7.6937</v>
+        <v>7.6908</v>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>skullz</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
@@ -38146,19 +38146,19 @@
         <v>29</v>
       </c>
       <c r="H849" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I849" t="n">
-        <v>0.2531</v>
+        <v>0.2652</v>
       </c>
       <c r="J849" t="n">
-        <v>7.3399</v>
+        <v>7.6908</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>skullz</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -38189,10 +38189,10 @@
         <v>1.16</v>
       </c>
       <c r="I850" t="n">
-        <v>0.2531</v>
+        <v>0.253</v>
       </c>
       <c r="J850" t="n">
-        <v>7.3399</v>
+        <v>7.337</v>
       </c>
     </row>
     <row r="851">
@@ -38229,10 +38229,10 @@
         <v>0.91</v>
       </c>
       <c r="I851" t="n">
-        <v>-0.1487</v>
+        <v>-0.1488</v>
       </c>
       <c r="J851" t="n">
-        <v>-4.3123</v>
+        <v>-4.3152</v>
       </c>
     </row>
     <row r="852">
@@ -39269,10 +39269,10 @@
         <v>1.35</v>
       </c>
       <c r="I877" t="n">
-        <v>0.8612</v>
+        <v>0.8617</v>
       </c>
       <c r="J877" t="n">
-        <v>18.9464</v>
+        <v>18.9574</v>
       </c>
     </row>
     <row r="878">
@@ -39309,10 +39309,10 @@
         <v>1.34</v>
       </c>
       <c r="I878" t="n">
-        <v>0.8413</v>
+        <v>0.8418</v>
       </c>
       <c r="J878" t="n">
-        <v>18.5086</v>
+        <v>18.5196</v>
       </c>
     </row>
     <row r="879">
@@ -39349,10 +39349,10 @@
         <v>1.14</v>
       </c>
       <c r="I879" t="n">
-        <v>0.4149</v>
+        <v>0.4151</v>
       </c>
       <c r="J879" t="n">
-        <v>9.127800000000001</v>
+        <v>9.132199999999999</v>
       </c>
     </row>
     <row r="880">
@@ -39389,10 +39389,10 @@
         <v>1</v>
       </c>
       <c r="I880" t="n">
-        <v>-0.0272</v>
+        <v>-0.0268</v>
       </c>
       <c r="J880" t="n">
-        <v>-0.5984</v>
+        <v>-0.5896</v>
       </c>
     </row>
     <row r="881">
@@ -39426,13 +39426,13 @@
         <v>22</v>
       </c>
       <c r="H881" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I881" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.1281</v>
       </c>
       <c r="J881" t="n">
-        <v>-1.914</v>
+        <v>-2.8182</v>
       </c>
     </row>
     <row r="882">
@@ -39669,10 +39669,10 @@
         <v>1.63</v>
       </c>
       <c r="I887" t="n">
-        <v>1.2336</v>
+        <v>1.2339</v>
       </c>
       <c r="J887" t="n">
-        <v>20.9712</v>
+        <v>20.9763</v>
       </c>
     </row>
     <row r="888">
@@ -39709,10 +39709,10 @@
         <v>1.54</v>
       </c>
       <c r="I888" t="n">
-        <v>1.1193</v>
+        <v>1.1195</v>
       </c>
       <c r="J888" t="n">
-        <v>19.0281</v>
+        <v>19.0315</v>
       </c>
     </row>
     <row r="889">
@@ -39746,13 +39746,13 @@
         <v>17</v>
       </c>
       <c r="H889" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I889" t="n">
-        <v>1.0805</v>
+        <v>1.0676</v>
       </c>
       <c r="J889" t="n">
-        <v>18.3685</v>
+        <v>18.1492</v>
       </c>
     </row>
     <row r="890">
@@ -39789,10 +39789,10 @@
         <v>1.48</v>
       </c>
       <c r="I890" t="n">
-        <v>1.0401</v>
+        <v>1.0403</v>
       </c>
       <c r="J890" t="n">
-        <v>17.6817</v>
+        <v>17.6851</v>
       </c>
     </row>
     <row r="891">
@@ -39829,10 +39829,10 @@
         <v>1.02</v>
       </c>
       <c r="I891" t="n">
-        <v>0.0299</v>
+        <v>0.0301</v>
       </c>
       <c r="J891" t="n">
-        <v>0.5083</v>
+        <v>0.5117</v>
       </c>
     </row>
     <row r="892">
@@ -40266,13 +40266,13 @@
         <v>23</v>
       </c>
       <c r="H902" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I902" t="n">
-        <v>0.3807</v>
+        <v>0.3971</v>
       </c>
       <c r="J902" t="n">
-        <v>8.7561</v>
+        <v>9.1333</v>
       </c>
     </row>
     <row r="903">
@@ -40309,10 +40309,10 @@
         <v>1.16</v>
       </c>
       <c r="I903" t="n">
-        <v>0.3807</v>
+        <v>0.379</v>
       </c>
       <c r="J903" t="n">
-        <v>8.7561</v>
+        <v>8.717000000000001</v>
       </c>
     </row>
     <row r="904">
@@ -40346,13 +40346,13 @@
         <v>23</v>
       </c>
       <c r="H904" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I904" t="n">
-        <v>-0.1185</v>
+        <v>-0.095</v>
       </c>
       <c r="J904" t="n">
-        <v>-2.7255</v>
+        <v>-2.185</v>
       </c>
     </row>
     <row r="905">
@@ -40389,10 +40389,10 @@
         <v>0.8</v>
       </c>
       <c r="I905" t="n">
-        <v>-0.246</v>
+        <v>-0.2466</v>
       </c>
       <c r="J905" t="n">
-        <v>-5.658</v>
+        <v>-5.6718</v>
       </c>
     </row>
     <row r="906">
@@ -40429,10 +40429,10 @@
         <v>0.62</v>
       </c>
       <c r="I906" t="n">
-        <v>-0.4137</v>
+        <v>-0.4142</v>
       </c>
       <c r="J906" t="n">
-        <v>-9.5151</v>
+        <v>-9.5266</v>
       </c>
     </row>
     <row r="907">
@@ -40469,10 +40469,10 @@
         <v>1.57</v>
       </c>
       <c r="I907" t="n">
-        <v>1.1912</v>
+        <v>1.1916</v>
       </c>
       <c r="J907" t="n">
-        <v>27.3976</v>
+        <v>27.4068</v>
       </c>
     </row>
     <row r="908">
@@ -40509,10 +40509,10 @@
         <v>1.35</v>
       </c>
       <c r="I908" t="n">
-        <v>0.8454</v>
+        <v>0.8458</v>
       </c>
       <c r="J908" t="n">
-        <v>19.4442</v>
+        <v>19.4534</v>
       </c>
     </row>
     <row r="909">
@@ -40546,13 +40546,13 @@
         <v>23</v>
       </c>
       <c r="H909" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I909" t="n">
-        <v>0.7466</v>
+        <v>0.7269</v>
       </c>
       <c r="J909" t="n">
-        <v>17.1718</v>
+        <v>16.7187</v>
       </c>
     </row>
     <row r="910">
@@ -40589,10 +40589,10 @@
         <v>1.15</v>
       </c>
       <c r="I910" t="n">
-        <v>0.4283</v>
+        <v>0.4286</v>
       </c>
       <c r="J910" t="n">
-        <v>9.850899999999999</v>
+        <v>9.857799999999999</v>
       </c>
     </row>
     <row r="911">
@@ -40629,10 +40629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I911" t="n">
-        <v>-0.6082</v>
+        <v>-0.6079</v>
       </c>
       <c r="J911" t="n">
-        <v>-13.9886</v>
+        <v>-13.9817</v>
       </c>
     </row>
     <row r="912">
@@ -41469,10 +41469,10 @@
         <v>1.03</v>
       </c>
       <c r="I932" t="n">
-        <v>0.0919</v>
+        <v>0.0916</v>
       </c>
       <c r="J932" t="n">
-        <v>1.838</v>
+        <v>1.832</v>
       </c>
     </row>
     <row r="933">
@@ -41509,10 +41509,10 @@
         <v>1.02</v>
       </c>
       <c r="I933" t="n">
-        <v>0.0704</v>
+        <v>0.0701</v>
       </c>
       <c r="J933" t="n">
-        <v>1.408</v>
+        <v>1.402</v>
       </c>
     </row>
     <row r="934">
@@ -41549,10 +41549,10 @@
         <v>0.96</v>
       </c>
       <c r="I934" t="n">
-        <v>-0.0658</v>
+        <v>-0.066</v>
       </c>
       <c r="J934" t="n">
-        <v>-1.316</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="935">
@@ -41586,13 +41586,13 @@
         <v>20</v>
       </c>
       <c r="H935" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I935" t="n">
-        <v>-0.2432</v>
+        <v>-0.2334</v>
       </c>
       <c r="J935" t="n">
-        <v>-4.864</v>
+        <v>-4.668</v>
       </c>
     </row>
     <row r="936">
@@ -41629,10 +41629,10 @@
         <v>0.7</v>
       </c>
       <c r="I936" t="n">
-        <v>-0.3384</v>
+        <v>-0.3386</v>
       </c>
       <c r="J936" t="n">
-        <v>-6.768</v>
+        <v>-6.772</v>
       </c>
     </row>
     <row r="937">
@@ -41869,10 +41869,10 @@
         <v>2.12</v>
       </c>
       <c r="I942" t="n">
-        <v>1.8039</v>
+        <v>1.8044</v>
       </c>
       <c r="J942" t="n">
-        <v>28.8624</v>
+        <v>28.8704</v>
       </c>
     </row>
     <row r="943">
@@ -41949,10 +41949,10 @@
         <v>1.4</v>
       </c>
       <c r="I944" t="n">
-        <v>0.9048</v>
+        <v>0.905</v>
       </c>
       <c r="J944" t="n">
-        <v>14.4768</v>
+        <v>14.48</v>
       </c>
     </row>
     <row r="945">
@@ -41986,13 +41986,13 @@
         <v>16</v>
       </c>
       <c r="H945" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I945" t="n">
-        <v>0.7519</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="J945" t="n">
-        <v>12.0304</v>
+        <v>11.7184</v>
       </c>
     </row>
     <row r="946">
@@ -42029,10 +42029,10 @@
         <v>1.2</v>
       </c>
       <c r="I946" t="n">
-        <v>0.5016</v>
+        <v>0.5019</v>
       </c>
       <c r="J946" t="n">
-        <v>8.025600000000001</v>
+        <v>8.0304</v>
       </c>
     </row>
     <row r="947">
@@ -42066,13 +42066,13 @@
         <v>16</v>
       </c>
       <c r="H947" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="I947" t="n">
-        <v>0.6538</v>
+        <v>0.669</v>
       </c>
       <c r="J947" t="n">
-        <v>10.4608</v>
+        <v>10.704</v>
       </c>
     </row>
     <row r="948">
@@ -42109,10 +42109,10 @@
         <v>0.76</v>
       </c>
       <c r="I948" t="n">
-        <v>-0.265</v>
+        <v>-0.2654</v>
       </c>
       <c r="J948" t="n">
-        <v>-4.24</v>
+        <v>-4.2464</v>
       </c>
     </row>
     <row r="949">
@@ -42149,10 +42149,10 @@
         <v>0.57</v>
       </c>
       <c r="I949" t="n">
-        <v>-0.435</v>
+        <v>-0.4355</v>
       </c>
       <c r="J949" t="n">
-        <v>-6.96</v>
+        <v>-6.968</v>
       </c>
     </row>
     <row r="950">
@@ -42189,10 +42189,10 @@
         <v>0.57</v>
       </c>
       <c r="I950" t="n">
-        <v>-0.435</v>
+        <v>-0.4355</v>
       </c>
       <c r="J950" t="n">
-        <v>-6.96</v>
+        <v>-6.968</v>
       </c>
     </row>
     <row r="951">
@@ -42226,13 +42226,13 @@
         <v>16</v>
       </c>
       <c r="H951" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="I951" t="n">
-        <v>-0.5487</v>
+        <v>-0.5405</v>
       </c>
       <c r="J951" t="n">
-        <v>-8.779199999999999</v>
+        <v>-8.648</v>
       </c>
     </row>
     <row r="952">
@@ -42269,10 +42269,10 @@
         <v>1.77</v>
       </c>
       <c r="I952" t="n">
-        <v>1.4497</v>
+        <v>1.4491</v>
       </c>
       <c r="J952" t="n">
-        <v>30.4437</v>
+        <v>30.4311</v>
       </c>
     </row>
     <row r="953">
@@ -42309,10 +42309,10 @@
         <v>1.34</v>
       </c>
       <c r="I953" t="n">
-        <v>0.8247</v>
+        <v>0.8243</v>
       </c>
       <c r="J953" t="n">
-        <v>17.3187</v>
+        <v>17.3103</v>
       </c>
     </row>
     <row r="954">
@@ -42346,13 +42346,13 @@
         <v>21</v>
       </c>
       <c r="H954" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I954" t="n">
-        <v>0.4964</v>
+        <v>0.5185</v>
       </c>
       <c r="J954" t="n">
-        <v>10.4244</v>
+        <v>10.8885</v>
       </c>
     </row>
     <row r="955">
@@ -42389,10 +42389,10 @@
         <v>1.04</v>
       </c>
       <c r="I955" t="n">
-        <v>0.1306</v>
+        <v>0.1303</v>
       </c>
       <c r="J955" t="n">
-        <v>2.7426</v>
+        <v>2.7363</v>
       </c>
     </row>
     <row r="956">
@@ -42429,10 +42429,10 @@
         <v>0.88</v>
       </c>
       <c r="I956" t="n">
-        <v>-0.4395</v>
+        <v>-0.4398</v>
       </c>
       <c r="J956" t="n">
-        <v>-9.2295</v>
+        <v>-9.235799999999999</v>
       </c>
     </row>
     <row r="957">
@@ -42469,10 +42469,10 @@
         <v>1.41</v>
       </c>
       <c r="I957" t="n">
-        <v>0.7623</v>
+        <v>0.7617</v>
       </c>
       <c r="J957" t="n">
-        <v>16.0083</v>
+        <v>15.9957</v>
       </c>
     </row>
     <row r="958">
@@ -42509,10 +42509,10 @@
         <v>1.17</v>
       </c>
       <c r="I958" t="n">
-        <v>0.3792</v>
+        <v>0.3788</v>
       </c>
       <c r="J958" t="n">
-        <v>7.9632</v>
+        <v>7.9548</v>
       </c>
     </row>
     <row r="959">
@@ -42549,10 +42549,10 @@
         <v>1.01</v>
       </c>
       <c r="I959" t="n">
-        <v>0.0425</v>
+        <v>0.0424</v>
       </c>
       <c r="J959" t="n">
-        <v>0.8925</v>
+        <v>0.8904</v>
       </c>
     </row>
     <row r="960">
@@ -42586,13 +42586,13 @@
         <v>21</v>
       </c>
       <c r="H960" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I960" t="n">
-        <v>-0.1704</v>
+        <v>-0.1594</v>
       </c>
       <c r="J960" t="n">
-        <v>-3.5784</v>
+        <v>-3.3474</v>
       </c>
     </row>
     <row r="961">
@@ -42629,10 +42629,10 @@
         <v>0.59</v>
       </c>
       <c r="I961" t="n">
-        <v>-0.4469</v>
+        <v>-0.4471</v>
       </c>
       <c r="J961" t="n">
-        <v>-9.3849</v>
+        <v>-9.389099999999999</v>
       </c>
     </row>
     <row r="962">
@@ -43069,10 +43069,10 @@
         <v>2.12</v>
       </c>
       <c r="I972" t="n">
-        <v>1.8419</v>
+        <v>1.8424</v>
       </c>
       <c r="J972" t="n">
-        <v>34.9961</v>
+        <v>35.0056</v>
       </c>
     </row>
     <row r="973">
@@ -43109,10 +43109,10 @@
         <v>1.54</v>
       </c>
       <c r="I973" t="n">
-        <v>1.1291</v>
+        <v>1.1294</v>
       </c>
       <c r="J973" t="n">
-        <v>21.4529</v>
+        <v>21.4586</v>
       </c>
     </row>
     <row r="974">
@@ -43146,13 +43146,13 @@
         <v>19</v>
       </c>
       <c r="H974" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="I974" t="n">
-        <v>0.9722</v>
+        <v>0.9556</v>
       </c>
       <c r="J974" t="n">
-        <v>18.4718</v>
+        <v>18.1564</v>
       </c>
     </row>
     <row r="975">
@@ -43189,10 +43189,10 @@
         <v>0.88</v>
       </c>
       <c r="I975" t="n">
-        <v>-0.4579</v>
+        <v>-0.4576</v>
       </c>
       <c r="J975" t="n">
-        <v>-8.700100000000001</v>
+        <v>-8.6944</v>
       </c>
     </row>
     <row r="976">
@@ -43229,10 +43229,10 @@
         <v>0.83</v>
       </c>
       <c r="I976" t="n">
-        <v>-0.5802</v>
+        <v>-0.5799</v>
       </c>
       <c r="J976" t="n">
-        <v>-11.0238</v>
+        <v>-11.0181</v>
       </c>
     </row>
     <row r="977">
